--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joaobiosmac/Desktop/Trabalhos &amp; Repositórios/Artigos em Andamento/Ilhas Amanda/Repo Amanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75681501-D3C6-D543-8178-26DC8256F365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11679BCE-9D0B-3D43-BF6C-220C17EDC568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="papers" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4757" uniqueCount="2621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4754" uniqueCount="2618">
   <si>
     <t xml:space="preserve">Bioinvasão </t>
   </si>
@@ -6128,9 +6128,6 @@
     <t>48°29'02.8"W</t>
   </si>
   <si>
-    <t>675.4</t>
-  </si>
-  <si>
     <t>IBGE</t>
   </si>
   <si>
@@ -7241,9 +7238,6 @@
     <t>63°27'31.6"W</t>
   </si>
   <si>
-    <t>5.660 </t>
-  </si>
-  <si>
     <t>University of Prince Edward Island</t>
   </si>
   <si>
@@ -7476,9 +7470,6 @@
   </si>
   <si>
     <t>1°16'03.8"W</t>
-  </si>
-  <si>
-    <t>1.46</t>
   </si>
   <si>
     <t xml:space="preserve">33°41'14.4"N </t>
@@ -7911,21 +7902,25 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -7973,9 +7968,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -7994,6 +7986,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8222,26 +8217,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
+        <v>2602</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>2603</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>2604</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>2605</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>2606</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>2607</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>2608</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>2609</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>2611</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>2612</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -19005,35 +19000,35 @@
       <c r="D1" s="1" t="s">
         <v>1803</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
+        <v>2610</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>2611</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>2607</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>2612</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>2613</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="J1" s="13" t="s">
         <v>2614</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>2610</v>
-      </c>
-      <c r="H1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>2615</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>2616</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>2617</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>2618</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>2619</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1804</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>2620</v>
+      <c r="N1" s="13" t="s">
+        <v>2617</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -19052,8 +19047,8 @@
       <c r="E2" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F2" s="7">
-        <v>1681</v>
+      <c r="F2" s="15">
+        <v>1141</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>1808</v>
@@ -19097,7 +19092,7 @@
         <v>1814</v>
       </c>
       <c r="F3" s="3">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>1815</v>
@@ -19140,8 +19135,8 @@
       <c r="E4" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F4" s="7">
-        <v>4264</v>
+      <c r="F4" s="15">
+        <v>4396</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>1815</v>
@@ -19185,7 +19180,7 @@
         <v>1814</v>
       </c>
       <c r="F5" s="3">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>1815</v>
@@ -19273,7 +19268,7 @@
         <v>1807</v>
       </c>
       <c r="F7" s="3">
-        <v>743</v>
+        <v>779</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>1815</v>
@@ -19316,8 +19311,8 @@
       <c r="E8" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F8" s="7">
-        <v>8249</v>
+      <c r="F8" s="15">
+        <v>2864</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>1836</v>
@@ -19360,8 +19355,8 @@
       <c r="E9" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F9" s="7">
-        <v>5957</v>
+      <c r="F9" s="15">
+        <v>3427</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>1808</v>
@@ -19405,7 +19400,7 @@
         <v>1814</v>
       </c>
       <c r="F10" s="3">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>1836</v>
@@ -19449,7 +19444,7 @@
         <v>1807</v>
       </c>
       <c r="F11" s="3">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>1850</v>
@@ -19463,7 +19458,7 @@
       <c r="J11" s="4" t="s">
         <v>1823</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="7" t="s">
         <v>1851</v>
       </c>
       <c r="L11" s="4">
@@ -19501,19 +19496,19 @@
       <c r="H12" s="3">
         <v>2</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <v>110000</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>1809</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="7" t="s">
         <v>1856</v>
       </c>
       <c r="L12" s="4">
         <v>100</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="7" t="s">
         <v>1857</v>
       </c>
       <c r="N12" s="4">
@@ -19537,7 +19532,7 @@
         <v>1814</v>
       </c>
       <c r="F13" s="3">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>1815</v>
@@ -19545,7 +19540,7 @@
       <c r="H13" s="3">
         <v>1</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <v>0</v>
       </c>
       <c r="J13" s="4" t="s">
@@ -19554,7 +19549,7 @@
       <c r="K13" s="4" t="s">
         <v>1816</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="7">
         <v>1005</v>
       </c>
       <c r="M13" s="4" t="s">
@@ -19580,8 +19575,8 @@
       <c r="E14" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F14" s="7">
-        <v>2351</v>
+      <c r="F14" s="15">
+        <v>140</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>1808</v>
@@ -19589,7 +19584,7 @@
       <c r="H14" s="3">
         <v>1</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <v>240000</v>
       </c>
       <c r="J14" s="5" t="s">
@@ -19668,8 +19663,8 @@
       <c r="E16" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F16" s="7">
-        <v>5636</v>
+      <c r="F16" s="15">
+        <v>5413</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>1836</v>
@@ -19677,7 +19672,7 @@
       <c r="H16" s="3">
         <v>6</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="7">
         <v>4500000</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -19712,8 +19707,8 @@
       <c r="E17" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F17" s="7">
-        <v>11910</v>
+      <c r="F17" s="15">
+        <v>11611</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>1836</v>
@@ -19721,7 +19716,7 @@
       <c r="H17" s="3">
         <v>17</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="7">
         <v>1300000</v>
       </c>
       <c r="J17" s="5" t="s">
@@ -19756,8 +19751,8 @@
       <c r="E18" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F18" s="7">
-        <v>1062</v>
+      <c r="F18" s="15">
+        <v>1034</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>1815</v>
@@ -19800,8 +19795,8 @@
       <c r="E19" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F19" s="7">
-        <v>4162</v>
+      <c r="F19" s="15">
+        <v>4224</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1815</v>
@@ -19809,7 +19804,7 @@
       <c r="H19" s="3">
         <v>2</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="7">
         <v>8500</v>
       </c>
       <c r="J19" s="5" t="s">
@@ -19853,7 +19848,7 @@
       <c r="H20" s="3">
         <v>1</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="7">
         <v>80000</v>
       </c>
       <c r="J20" s="5" t="s">
@@ -19889,7 +19884,7 @@
         <v>1807</v>
       </c>
       <c r="F21" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>1850</v>
@@ -19932,8 +19927,8 @@
       <c r="E22" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F22" s="7">
-        <v>4859</v>
+      <c r="F22" s="15">
+        <v>4642</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>1815</v>
@@ -19941,7 +19936,7 @@
       <c r="H22" s="3">
         <v>8</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="7">
         <v>350000</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -19976,8 +19971,8 @@
       <c r="E23" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F23" s="7">
-        <v>1187</v>
+      <c r="F23" s="15">
+        <v>1173</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>1815</v>
@@ -20020,8 +20015,8 @@
       <c r="E24" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F24" s="7">
-        <v>2017</v>
+      <c r="F24" s="15">
+        <v>1949</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>1808</v>
@@ -20029,7 +20024,7 @@
       <c r="H24" s="3">
         <v>1</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="7">
         <v>350000</v>
       </c>
       <c r="J24" s="5" t="s">
@@ -20065,7 +20060,7 @@
         <v>1807</v>
       </c>
       <c r="F25" s="3">
-        <v>16.899999999999999</v>
+        <v>17</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>1815</v>
@@ -20109,7 +20104,7 @@
         <v>1814</v>
       </c>
       <c r="F26" s="3">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>1808</v>
@@ -20117,7 +20112,7 @@
       <c r="H26" s="3">
         <v>1</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="7">
         <v>15000</v>
       </c>
       <c r="J26" s="5" t="s">
@@ -20153,7 +20148,7 @@
         <v>1807</v>
       </c>
       <c r="F27" s="3">
-        <v>89.6</v>
+        <v>72</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>1815</v>
@@ -20170,7 +20165,7 @@
       <c r="K27" s="4" t="s">
         <v>1869</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="7">
         <v>540</v>
       </c>
       <c r="M27" s="4" t="s">
@@ -20197,7 +20192,7 @@
         <v>1807</v>
       </c>
       <c r="F28" s="3">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>1850</v>
@@ -20205,19 +20200,19 @@
       <c r="H28" s="3">
         <v>4</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="7">
         <v>900</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>1809</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="K28" s="7" t="s">
         <v>1851</v>
       </c>
       <c r="L28" s="4">
         <v>235</v>
       </c>
-      <c r="M28" s="8" t="s">
+      <c r="M28" s="7" t="s">
         <v>1852</v>
       </c>
       <c r="N28" s="4">
@@ -20241,7 +20236,7 @@
         <v>1807</v>
       </c>
       <c r="F29" s="3">
-        <v>288</v>
+        <v>243</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>1808</v>
@@ -20249,7 +20244,7 @@
       <c r="H29" s="3">
         <v>2</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="7">
         <v>21000</v>
       </c>
       <c r="J29" s="5" t="s">
@@ -20284,8 +20279,8 @@
       <c r="E30" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F30" s="7">
-        <v>9318</v>
+      <c r="F30" s="15">
+        <v>8750</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>1815</v>
@@ -20293,7 +20288,7 @@
       <c r="H30" s="3">
         <v>3</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="7">
         <v>370000</v>
       </c>
       <c r="J30" s="5" t="s">
@@ -20328,8 +20323,8 @@
       <c r="E31" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F31" s="7">
-        <v>4727</v>
+      <c r="F31" s="15">
+        <v>4534</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>1815</v>
@@ -20337,7 +20332,7 @@
       <c r="H31" s="3">
         <v>1</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="7">
         <v>415000</v>
       </c>
       <c r="J31" s="5" t="s">
@@ -20372,8 +20367,8 @@
       <c r="E32" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F32" s="7">
-        <v>10311</v>
+      <c r="F32" s="15">
+        <v>10513</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>1808</v>
@@ -20381,7 +20376,7 @@
       <c r="H32" s="3">
         <v>3</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="7">
         <v>135000</v>
       </c>
       <c r="J32" s="5" t="s">
@@ -20417,7 +20412,7 @@
         <v>1814</v>
       </c>
       <c r="F33" s="3">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>1836</v>
@@ -20425,7 +20420,7 @@
       <c r="H33" s="3">
         <v>2</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="7">
         <v>17800</v>
       </c>
       <c r="J33" s="5" t="s">
@@ -20460,8 +20455,8 @@
       <c r="E34" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F34" s="7">
-        <v>17100</v>
+      <c r="F34" s="15">
+        <v>17510</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>1815</v>
@@ -20469,7 +20464,7 @@
       <c r="H34" s="3">
         <v>1</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="7">
         <v>773000</v>
       </c>
       <c r="J34" s="5" t="s">
@@ -20505,7 +20500,7 @@
         <v>1807</v>
       </c>
       <c r="F35" s="3">
-        <v>966</v>
+        <v>923</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>1815</v>
@@ -20548,8 +20543,8 @@
       <c r="E36" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F36" s="7">
-        <v>5305</v>
+      <c r="F36" s="15">
+        <v>5393</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>1815</v>
@@ -20557,7 +20552,7 @@
       <c r="H36" s="3">
         <v>1</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="7">
         <v>1300</v>
       </c>
       <c r="J36" s="5" t="s">
@@ -20592,8 +20587,8 @@
       <c r="E37" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F37" s="7">
-        <v>8394</v>
+      <c r="F37" s="15">
+        <v>8320</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>1808</v>
@@ -20601,7 +20596,7 @@
       <c r="H37" s="3">
         <v>2</v>
       </c>
-      <c r="I37" s="8">
+      <c r="I37" s="7">
         <v>168000</v>
       </c>
       <c r="J37" s="5" t="s">
@@ -20636,8 +20631,8 @@
       <c r="E38" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F38" s="7">
-        <v>9251</v>
+      <c r="F38" s="15">
+        <v>9283</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>1808</v>
@@ -20645,7 +20640,7 @@
       <c r="H38" s="3">
         <v>3</v>
       </c>
-      <c r="I38" s="8">
+      <c r="I38" s="7">
         <v>1190000</v>
       </c>
       <c r="J38" s="5" t="s">
@@ -20680,8 +20675,8 @@
       <c r="E39" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F39" s="7">
-        <v>3837</v>
+      <c r="F39" s="15">
+        <v>3126</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>1815</v>
@@ -20689,7 +20684,7 @@
       <c r="H39" s="3">
         <v>3</v>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="7">
         <v>26400</v>
       </c>
       <c r="J39" s="5" t="s">
@@ -20725,7 +20720,7 @@
         <v>1814</v>
       </c>
       <c r="F40" s="3">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>1815</v>
@@ -20733,7 +20728,7 @@
       <c r="H40" s="3">
         <v>1</v>
       </c>
-      <c r="I40" s="8">
+      <c r="I40" s="7">
         <v>50000</v>
       </c>
       <c r="J40" s="5" t="s">
@@ -20769,7 +20764,7 @@
         <v>1814</v>
       </c>
       <c r="F41" s="3">
-        <v>23.85</v>
+        <v>23</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>1815</v>
@@ -20812,8 +20807,8 @@
       <c r="E42" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F42" s="7">
-        <v>2235</v>
+      <c r="F42" s="15">
+        <v>1018</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>1836</v>
@@ -20821,7 +20816,7 @@
       <c r="H42" s="3">
         <v>1</v>
       </c>
-      <c r="I42" s="8">
+      <c r="I42" s="7">
         <v>850000</v>
       </c>
       <c r="J42" s="5" t="s">
@@ -20857,7 +20852,7 @@
         <v>1807</v>
       </c>
       <c r="F43" s="3">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>1808</v>
@@ -20865,7 +20860,7 @@
       <c r="H43" s="3">
         <v>2</v>
       </c>
-      <c r="I43" s="8">
+      <c r="I43" s="7">
         <v>112000</v>
       </c>
       <c r="J43" s="5" t="s">
@@ -20900,8 +20895,8 @@
       <c r="E44" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F44" s="7">
-        <v>6995</v>
+      <c r="F44" s="15">
+        <v>7070</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>1850</v>
@@ -20944,8 +20939,8 @@
       <c r="E45" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F45" s="7">
-        <v>8722</v>
+      <c r="F45" s="15">
+        <v>8729</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>1808</v>
@@ -20953,7 +20948,7 @@
       <c r="H45" s="3">
         <v>6</v>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="7">
         <v>355000</v>
       </c>
       <c r="J45" s="5" t="s">
@@ -20989,7 +20984,7 @@
         <v>1807</v>
       </c>
       <c r="F46" s="3">
-        <v>647.33000000000004</v>
+        <v>483</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>1808</v>
@@ -20997,7 +20992,7 @@
       <c r="H46" s="3">
         <v>1</v>
       </c>
-      <c r="I46" s="8">
+      <c r="I46" s="7">
         <v>100000</v>
       </c>
       <c r="J46" s="5" t="s">
@@ -21033,7 +21028,7 @@
         <v>1807</v>
       </c>
       <c r="F47" s="3">
-        <v>405</v>
+        <v>485</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>1808</v>
@@ -21041,7 +21036,7 @@
       <c r="H47" s="3">
         <v>3</v>
       </c>
-      <c r="I47" s="8">
+      <c r="I47" s="7">
         <v>3000</v>
       </c>
       <c r="J47" s="5" t="s">
@@ -21076,8 +21071,8 @@
       <c r="E48" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F48" s="7">
-        <v>8336</v>
+      <c r="F48" s="15">
+        <v>8296</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>1808</v>
@@ -21085,7 +21080,7 @@
       <c r="H48" s="3">
         <v>1</v>
       </c>
-      <c r="I48" s="8">
+      <c r="I48" s="7">
         <v>630000</v>
       </c>
       <c r="J48" s="5" t="s">
@@ -21121,7 +21116,7 @@
         <v>1807</v>
       </c>
       <c r="F49" s="3">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>1808</v>
@@ -21129,7 +21124,7 @@
       <c r="H49" s="3">
         <v>2</v>
       </c>
-      <c r="I49" s="8">
+      <c r="I49" s="7">
         <v>180000</v>
       </c>
       <c r="J49" s="5" t="s">
@@ -21173,7 +21168,7 @@
       <c r="H50" s="3">
         <v>2</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="8">
         <v>0</v>
       </c>
       <c r="J50" s="4" t="s">
@@ -21209,7 +21204,7 @@
         <v>1814</v>
       </c>
       <c r="F51" s="3">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>1808</v>
@@ -21217,7 +21212,7 @@
       <c r="H51" s="3">
         <v>1</v>
       </c>
-      <c r="I51" s="8">
+      <c r="I51" s="7">
         <v>65000</v>
       </c>
       <c r="J51" s="5" t="s">
@@ -21261,7 +21256,7 @@
       <c r="H52" s="3">
         <v>2</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="7">
         <v>5200</v>
       </c>
       <c r="J52" s="5" t="s">
@@ -21270,7 +21265,7 @@
       <c r="K52" s="4" t="s">
         <v>2015</v>
       </c>
-      <c r="L52" s="8">
+      <c r="L52" s="7">
         <v>1090</v>
       </c>
       <c r="M52" s="4" t="s">
@@ -21296,8 +21291,8 @@
       <c r="E53" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F53" s="7">
-        <v>3655</v>
+      <c r="F53" s="15">
+        <v>3667</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>1808</v>
@@ -21305,7 +21300,7 @@
       <c r="H53" s="3">
         <v>2</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="7">
         <v>200000</v>
       </c>
       <c r="J53" s="5" t="s">
@@ -21340,7 +21335,7 @@
       <c r="E54" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54" s="15">
         <v>1399</v>
       </c>
       <c r="G54" s="4" t="s">
@@ -21349,7 +21344,7 @@
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="8">
+      <c r="I54" s="7">
         <v>56500</v>
       </c>
       <c r="J54" s="5" t="s">
@@ -21402,7 +21397,7 @@
       <c r="K55" s="4" t="s">
         <v>2028</v>
       </c>
-      <c r="L55" s="8">
+      <c r="L55" s="7">
         <v>1420</v>
       </c>
       <c r="M55" s="4" t="s">
@@ -21428,8 +21423,8 @@
       <c r="E56" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>2032</v>
+      <c r="F56" s="3">
+        <v>423</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>1808</v>
@@ -21437,20 +21432,20 @@
       <c r="H56" s="3">
         <v>2</v>
       </c>
-      <c r="I56" s="8">
+      <c r="I56" s="7">
         <v>537000</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="L56" s="4">
         <v>0</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="N56" s="4">
         <v>2</v>
@@ -21464,16 +21459,16 @@
         <v>1180</v>
       </c>
       <c r="C57" s="4" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>2035</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>2036</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F57" s="7">
-        <v>1840</v>
+      <c r="F57" s="15">
+        <v>1672</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>1815</v>
@@ -21494,7 +21489,7 @@
         <v>30</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="N57" s="4">
         <v>7</v>
@@ -21502,22 +21497,22 @@
     </row>
     <row r="58" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C58" s="4" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>2039</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>2040</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F58" s="3">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>1815</v>
@@ -21525,7 +21520,7 @@
       <c r="H58" s="3">
         <v>2</v>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="7">
         <v>3500</v>
       </c>
       <c r="J58" s="5" t="s">
@@ -21538,7 +21533,7 @@
         <v>560</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="N58" s="4">
         <v>3</v>
@@ -21552,16 +21547,16 @@
         <v>910</v>
       </c>
       <c r="C59" s="4" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>2042</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>2043</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F59" s="3">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>1815</v>
@@ -21569,20 +21564,20 @@
       <c r="H59" s="3">
         <v>4</v>
       </c>
-      <c r="I59" s="8">
+      <c r="I59" s="7">
         <v>3000</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="L59" s="4">
         <v>140</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="N59" s="4">
         <v>4</v>
@@ -21596,16 +21591,16 @@
         <v>141</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>2046</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>2047</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F60" s="3">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>1815</v>
@@ -21613,20 +21608,20 @@
       <c r="H60" s="3">
         <v>1</v>
       </c>
-      <c r="I60" s="8">
+      <c r="I60" s="7">
         <v>5000</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="L60" s="4">
         <v>63</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="N60" s="4">
         <v>1</v>
@@ -21640,16 +21635,16 @@
         <v>141</v>
       </c>
       <c r="C61" s="4" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>2050</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>2051</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F61" s="3">
-        <v>383.4</v>
+        <v>388</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>1815</v>
@@ -21657,20 +21652,20 @@
       <c r="H61" s="3">
         <v>3</v>
       </c>
-      <c r="I61" s="8">
+      <c r="I61" s="7">
         <v>245000</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="L61" s="4">
         <v>60</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="N61" s="4">
         <v>5</v>
@@ -21684,16 +21679,16 @@
         <v>272</v>
       </c>
       <c r="C62" s="4" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>2053</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>2054</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F62" s="3">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>1808</v>
@@ -21701,20 +21696,20 @@
       <c r="H62" s="3">
         <v>2</v>
       </c>
-      <c r="I62" s="8">
+      <c r="I62" s="7">
         <v>10000</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="L62" s="4">
         <v>0</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="N62" s="4">
         <v>9</v>
@@ -21728,16 +21723,16 @@
         <v>1473</v>
       </c>
       <c r="C63" s="4" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>2057</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>2058</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F63" s="3">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>1815</v>
@@ -21752,13 +21747,13 @@
         <v>1823</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="L63" s="4">
         <v>190</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="N63" s="4">
         <v>1</v>
@@ -21766,22 +21761,22 @@
     </row>
     <row r="64" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C64" s="4" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>2062</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>2063</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F64" s="7">
-        <v>16372</v>
+      <c r="F64" s="15">
+        <v>16368</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>1815</v>
@@ -21789,20 +21784,20 @@
       <c r="H64" s="3">
         <v>9</v>
       </c>
-      <c r="I64" s="8">
+      <c r="I64" s="7">
         <v>270000</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="L64" s="4">
         <v>0</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="N64" s="4">
         <v>9</v>
@@ -21816,16 +21811,16 @@
         <v>42</v>
       </c>
       <c r="C65" s="4" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>2066</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>2067</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F65" s="7">
-        <v>1628</v>
+      <c r="F65" s="15">
+        <v>1451</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>1808</v>
@@ -21833,7 +21828,7 @@
       <c r="H65" s="3">
         <v>13</v>
       </c>
-      <c r="I65" s="8">
+      <c r="I65" s="7">
         <v>380000</v>
       </c>
       <c r="J65" s="5" t="s">
@@ -21846,7 +21841,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="N65" s="4">
         <v>18</v>
@@ -21860,16 +21855,16 @@
         <v>26</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>2069</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>2070</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F66" s="3">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>1815</v>
@@ -21877,7 +21872,7 @@
       <c r="H66" s="3">
         <v>2</v>
       </c>
-      <c r="I66" s="8">
+      <c r="I66" s="7">
         <v>153000</v>
       </c>
       <c r="J66" s="5" t="s">
@@ -21890,7 +21885,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="N66" s="4">
         <v>10</v>
@@ -21898,22 +21893,22 @@
     </row>
     <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>1233</v>
       </c>
       <c r="C67" s="4" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>2073</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>2074</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F67" s="3">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>1808</v>
@@ -21921,20 +21916,20 @@
       <c r="H67" s="3">
         <v>1</v>
       </c>
-      <c r="I67" s="8">
+      <c r="I67" s="7">
         <v>6000</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="L67" s="4">
         <v>130</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="N67" s="4">
         <v>22</v>
@@ -21948,15 +21943,15 @@
         <v>69</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>2077</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>2078</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68" s="15">
         <v>10180</v>
       </c>
       <c r="G68" s="4" t="s">
@@ -21965,7 +21960,7 @@
       <c r="H68" s="3">
         <v>20</v>
       </c>
-      <c r="I68" s="8">
+      <c r="I68" s="7">
         <v>5000</v>
       </c>
       <c r="J68" s="5" t="s">
@@ -21978,7 +21973,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="N68" s="4">
         <v>3</v>
@@ -21992,16 +21987,16 @@
         <v>528</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>2080</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>2081</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F69" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>1808</v>
@@ -22009,20 +22004,20 @@
       <c r="H69" s="3">
         <v>1</v>
       </c>
-      <c r="I69" s="8">
+      <c r="I69" s="7">
         <v>1800</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="L69" s="4">
         <v>87</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="N69" s="4">
         <v>1</v>
@@ -22036,16 +22031,16 @@
         <v>26</v>
       </c>
       <c r="C70" s="4" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>2084</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>2085</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F70" s="7">
-        <v>10438</v>
+      <c r="F70" s="15">
+        <v>10492</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>1815</v>
@@ -22053,7 +22048,7 @@
       <c r="H70" s="3">
         <v>37</v>
       </c>
-      <c r="I70" s="8">
+      <c r="I70" s="7">
         <v>200000</v>
       </c>
       <c r="J70" s="5" t="s">
@@ -22066,7 +22061,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="N70" s="4">
         <v>36</v>
@@ -22074,16 +22069,16 @@
     </row>
     <row r="71" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>1103</v>
       </c>
       <c r="C71" s="4" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>2088</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>2089</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>1807</v>
@@ -22118,16 +22113,16 @@
     </row>
     <row r="72" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>1254</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>2091</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>2092</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>1814</v>
@@ -22141,20 +22136,20 @@
       <c r="H72" s="3">
         <v>1</v>
       </c>
-      <c r="I72" s="8">
+      <c r="I72" s="7">
         <v>600</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K72" s="4" t="s">
+        <v>2092</v>
+      </c>
+      <c r="L72" s="7">
+        <v>1510</v>
+      </c>
+      <c r="M72" s="4" t="s">
         <v>2093</v>
-      </c>
-      <c r="L72" s="8">
-        <v>1510</v>
-      </c>
-      <c r="M72" s="4" t="s">
-        <v>2094</v>
       </c>
       <c r="N72" s="4">
         <v>9</v>
@@ -22168,10 +22163,10 @@
         <v>69</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>2095</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>2096</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>1807</v>
@@ -22185,7 +22180,7 @@
       <c r="H73" s="3">
         <v>1</v>
       </c>
-      <c r="I73" s="8">
+      <c r="I73" s="7">
         <v>2000</v>
       </c>
       <c r="J73" s="5" t="s">
@@ -22206,16 +22201,16 @@
     </row>
     <row r="74" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>2098</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>2099</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>1814</v>
@@ -22229,7 +22224,7 @@
       <c r="H74" s="3">
         <v>1</v>
       </c>
-      <c r="I74" s="8">
+      <c r="I74" s="7">
         <v>1200</v>
       </c>
       <c r="J74" s="5" t="s">
@@ -22256,10 +22251,10 @@
         <v>32</v>
       </c>
       <c r="C75" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>2100</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>2101</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>1807</v>
@@ -22273,7 +22268,7 @@
       <c r="H75" s="3">
         <v>3</v>
       </c>
-      <c r="I75" s="8">
+      <c r="I75" s="7">
         <v>26000</v>
       </c>
       <c r="J75" s="5" t="s">
@@ -22286,7 +22281,7 @@
         <v>110</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="N75" s="4">
         <v>3</v>
@@ -22300,10 +22295,10 @@
         <v>74</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>2103</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>2104</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>1807</v>
@@ -22317,20 +22312,20 @@
       <c r="H76" s="3">
         <v>1</v>
       </c>
-      <c r="I76" s="8">
+      <c r="I76" s="7">
         <v>5000</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="L76" s="4">
         <v>110</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="N76" s="4">
         <v>14</v>
@@ -22344,10 +22339,10 @@
         <v>32</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>2106</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>2107</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>1814</v>
@@ -22361,7 +22356,7 @@
       <c r="H77" s="3">
         <v>6</v>
       </c>
-      <c r="I77" s="8">
+      <c r="I77" s="7">
         <v>2500</v>
       </c>
       <c r="J77" s="5" t="s">
@@ -22374,7 +22369,7 @@
         <v>225</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="N77" s="4">
         <v>6</v>
@@ -22382,21 +22377,21 @@
     </row>
     <row r="78" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>247</v>
       </c>
       <c r="C78" s="4" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>2110</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>2111</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F78" s="15">
         <v>4136</v>
       </c>
       <c r="G78" s="4" t="s">
@@ -22405,7 +22400,7 @@
       <c r="H78" s="3">
         <v>1</v>
       </c>
-      <c r="I78" s="8">
+      <c r="I78" s="7">
         <v>30000</v>
       </c>
       <c r="J78" s="5" t="s">
@@ -22426,16 +22421,16 @@
     </row>
     <row r="79" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C79" s="4" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>2113</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>2114</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>1814</v>
@@ -22449,7 +22444,7 @@
       <c r="H79" s="3">
         <v>3</v>
       </c>
-      <c r="I79" s="8">
+      <c r="I79" s="7">
         <v>50000</v>
       </c>
       <c r="J79" s="5" t="s">
@@ -22462,7 +22457,7 @@
         <v>0</v>
       </c>
       <c r="M79" s="4" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="N79" s="4">
         <v>3</v>
@@ -22476,15 +22471,15 @@
         <v>737</v>
       </c>
       <c r="C80" s="2" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>2116</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>2117</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80" s="15">
         <v>2419</v>
       </c>
       <c r="G80" s="4" t="s">
@@ -22493,20 +22488,20 @@
       <c r="H80" s="3">
         <v>2</v>
       </c>
-      <c r="I80" s="8">
+      <c r="I80" s="7">
         <v>85000</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="L80" s="4">
         <v>0</v>
       </c>
       <c r="M80" s="4" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="N80" s="4">
         <v>1</v>
@@ -22520,15 +22515,15 @@
         <v>19</v>
       </c>
       <c r="C81" s="2" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>2120</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>2121</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F81" s="7">
+      <c r="F81" s="15">
         <v>3139</v>
       </c>
       <c r="G81" s="4" t="s">
@@ -22537,20 +22532,20 @@
       <c r="H81" s="3">
         <v>10</v>
       </c>
-      <c r="I81" s="8">
+      <c r="I81" s="7">
         <v>7000</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="L81" s="4">
         <v>440</v>
       </c>
       <c r="M81" s="4" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="N81" s="4">
         <v>5</v>
@@ -22558,16 +22553,16 @@
     </row>
     <row r="82" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C82" s="4" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>2125</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>2126</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>1814</v>
@@ -22581,14 +22576,14 @@
       <c r="H82" s="3">
         <v>1</v>
       </c>
-      <c r="I82" s="8">
+      <c r="I82" s="7">
         <v>1400</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="L82" s="4">
         <v>77</v>
@@ -22602,21 +22597,21 @@
     </row>
     <row r="83" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>2128</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>2128</v>
-      </c>
-      <c r="C83" s="4" t="s">
+      <c r="D83" s="4" t="s">
         <v>2129</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>2130</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F83" s="7">
+      <c r="F83" s="15">
         <v>10990</v>
       </c>
       <c r="G83" s="4" t="s">
@@ -22625,20 +22620,20 @@
       <c r="H83" s="3">
         <v>1</v>
       </c>
-      <c r="I83" s="8">
+      <c r="I83" s="7">
         <v>2900000</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="L83" s="4">
         <v>0</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="N83" s="4">
         <v>1</v>
@@ -22652,10 +22647,10 @@
         <v>141</v>
       </c>
       <c r="C84" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>2133</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>2134</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>1807</v>
@@ -22669,20 +22664,20 @@
       <c r="H84" s="3">
         <v>1</v>
       </c>
-      <c r="I84" s="8">
+      <c r="I84" s="7">
         <v>30000</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="L84" s="4">
         <v>100</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="N84" s="4">
         <v>1</v>
@@ -22690,16 +22685,16 @@
     </row>
     <row r="85" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C85" s="2" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>2138</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2139</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>1807</v>
@@ -22713,7 +22708,7 @@
       <c r="H85" s="3">
         <v>1</v>
       </c>
-      <c r="I85" s="8">
+      <c r="I85" s="7">
         <v>40000</v>
       </c>
       <c r="J85" s="5" t="s">
@@ -22726,7 +22721,7 @@
         <v>75</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="N85" s="4">
         <v>15</v>
@@ -22734,21 +22729,21 @@
     </row>
     <row r="86" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C86" s="4" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>2142</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>2143</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F86" s="15">
         <v>116</v>
       </c>
       <c r="G86" s="4" t="s">
@@ -22757,7 +22752,7 @@
       <c r="H86" s="3">
         <v>1</v>
       </c>
-      <c r="I86" s="8">
+      <c r="I86" s="7">
         <v>0</v>
       </c>
       <c r="J86" s="4" t="s">
@@ -22770,7 +22765,7 @@
         <v>40</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="N86" s="4">
         <v>1</v>
@@ -22778,16 +22773,16 @@
     </row>
     <row r="87" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C87" s="2" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>2146</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>2147</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>1814</v>
@@ -22808,9 +22803,9 @@
         <v>1823</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>2148</v>
-      </c>
-      <c r="L87" s="8">
+        <v>2147</v>
+      </c>
+      <c r="L87" s="7">
         <v>1639</v>
       </c>
       <c r="M87" s="4" t="s">
@@ -22822,21 +22817,21 @@
     </row>
     <row r="88" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>1254</v>
       </c>
       <c r="C88" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>2150</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>2151</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F88" s="7">
+      <c r="F88" s="15">
         <v>1.1000000000000001</v>
       </c>
       <c r="G88" s="2" t="s">
@@ -22845,22 +22840,22 @@
       <c r="H88" s="3">
         <v>1</v>
       </c>
-      <c r="I88" s="10">
+      <c r="I88" s="9">
         <v>500</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>2152</v>
-      </c>
-      <c r="L88" s="9">
+        <v>2151</v>
+      </c>
+      <c r="L88" s="8">
         <v>760</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>2094</v>
-      </c>
-      <c r="N88" s="9">
+        <v>2093</v>
+      </c>
+      <c r="N88" s="8">
         <v>9</v>
       </c>
     </row>
@@ -22872,16 +22867,16 @@
         <v>26</v>
       </c>
       <c r="C89" s="4" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>2153</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>2154</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F89" s="7">
-        <v>1456</v>
+      <c r="F89" s="15">
+        <v>1445</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>1815</v>
@@ -22889,7 +22884,7 @@
       <c r="H89" s="3">
         <v>20</v>
       </c>
-      <c r="I89" s="8">
+      <c r="I89" s="7">
         <v>75000</v>
       </c>
       <c r="J89" s="5" t="s">
@@ -22902,7 +22897,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="N89" s="4">
         <v>25</v>
@@ -22916,21 +22911,21 @@
         <v>42</v>
       </c>
       <c r="C90" s="2" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>2156</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>2157</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F90" s="7">
+      <c r="F90" s="15">
         <v>7215</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>1836</v>
       </c>
-      <c r="H90" s="11">
+      <c r="H90" s="10">
         <v>11</v>
       </c>
       <c r="I90" s="4">
@@ -22940,13 +22935,13 @@
         <v>1823</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="L90" s="4">
         <v>0</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="N90" s="4">
         <v>3</v>
@@ -22960,10 +22955,10 @@
         <v>636</v>
       </c>
       <c r="C91" s="2" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>2160</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>2161</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>1807</v>
@@ -22984,13 +22979,13 @@
         <v>1809</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="L91" s="4">
         <v>145</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="N91" s="4">
         <v>3</v>
@@ -22998,16 +22993,16 @@
     </row>
     <row r="92" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C92" s="2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>2165</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>2166</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>1814</v>
@@ -23021,7 +23016,7 @@
       <c r="H92" s="3">
         <v>1</v>
       </c>
-      <c r="I92" s="8">
+      <c r="I92" s="7">
         <v>7000</v>
       </c>
       <c r="J92" s="5" t="s">
@@ -23048,15 +23043,15 @@
         <v>69</v>
       </c>
       <c r="C93" s="2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>2167</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>2168</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F93" s="7">
+      <c r="F93" s="15">
         <v>13111</v>
       </c>
       <c r="G93" s="4" t="s">
@@ -23065,7 +23060,7 @@
       <c r="H93" s="3">
         <v>1</v>
       </c>
-      <c r="I93" s="8">
+      <c r="I93" s="7">
         <v>1300</v>
       </c>
       <c r="J93" s="5" t="s">
@@ -23092,10 +23087,10 @@
         <v>852</v>
       </c>
       <c r="C94" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>2169</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>2170</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>1807</v>
@@ -23109,20 +23104,20 @@
       <c r="H94" s="3">
         <v>1</v>
       </c>
-      <c r="I94" s="8">
+      <c r="I94" s="7">
         <v>140000</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="L94" s="4">
         <v>0</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="N94" s="4">
         <v>18</v>
@@ -23130,16 +23125,16 @@
     </row>
     <row r="95" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C95" s="2" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>2174</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>2175</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>1814</v>
@@ -23160,9 +23155,9 @@
         <v>1823</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>2176</v>
-      </c>
-      <c r="L95" s="8">
+        <v>2175</v>
+      </c>
+      <c r="L95" s="7">
         <v>1275</v>
       </c>
       <c r="M95" s="4" t="s">
@@ -23180,15 +23175,15 @@
         <v>26</v>
       </c>
       <c r="C96" s="4" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>2177</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>2178</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F96" s="7">
+      <c r="F96" s="15">
         <v>9311</v>
       </c>
       <c r="G96" s="4" t="s">
@@ -23197,20 +23192,20 @@
       <c r="H96" s="3">
         <v>3</v>
       </c>
-      <c r="I96" s="8">
+      <c r="I96" s="7">
         <v>13000</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L96" s="4">
         <v>0</v>
       </c>
       <c r="M96" s="4" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="N96" s="4">
         <v>2</v>
@@ -23224,15 +23219,15 @@
         <v>19</v>
       </c>
       <c r="C97" s="2" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>2180</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>2181</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F97" s="7">
+      <c r="F97" s="15">
         <v>4968</v>
       </c>
       <c r="G97" s="4" t="s">
@@ -23248,7 +23243,7 @@
         <v>1809</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="L97" s="4">
         <v>630</v>
@@ -23262,16 +23257,16 @@
     </row>
     <row r="98" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C98" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>2183</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>2184</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>1814</v>
@@ -23285,7 +23280,7 @@
       <c r="H98" s="3">
         <v>3</v>
       </c>
-      <c r="I98" s="8">
+      <c r="I98" s="7">
         <v>6000</v>
       </c>
       <c r="J98" s="5" t="s">
@@ -23309,13 +23304,13 @@
         <v>1255</v>
       </c>
       <c r="B99" s="4" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>2185</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="D99" s="4" t="s">
         <v>2186</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>2187</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>1814</v>
@@ -23329,20 +23324,20 @@
       <c r="H99" s="3">
         <v>3</v>
       </c>
-      <c r="I99" s="8">
+      <c r="I99" s="7">
         <v>6600</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="L99" s="4">
         <v>557</v>
       </c>
       <c r="M99" s="4" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="N99" s="4">
         <v>31</v>
@@ -23356,10 +23351,10 @@
         <v>19</v>
       </c>
       <c r="C100" s="2" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>2188</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>2189</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>1807</v>
@@ -23373,20 +23368,20 @@
       <c r="H100" s="3">
         <v>1</v>
       </c>
-      <c r="I100" s="8">
+      <c r="I100" s="7">
         <v>45000</v>
       </c>
       <c r="J100" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="L100" s="4">
         <v>30</v>
       </c>
       <c r="M100" s="4" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="N100" s="4">
         <v>1</v>
@@ -23400,10 +23395,10 @@
         <v>91</v>
       </c>
       <c r="C101" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>2192</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>2193</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>1807</v>
@@ -23417,7 +23412,7 @@
       <c r="H101" s="3">
         <v>2</v>
       </c>
-      <c r="I101" s="8">
+      <c r="I101" s="7">
         <v>20000</v>
       </c>
       <c r="J101" s="5" t="s">
@@ -23430,7 +23425,7 @@
         <v>40</v>
       </c>
       <c r="M101" s="4" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="N101" s="4">
         <v>2</v>
@@ -23438,16 +23433,16 @@
     </row>
     <row r="102" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C102" s="2" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>2196</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>2197</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>1814</v>
@@ -23461,7 +23456,7 @@
       <c r="H102" s="3">
         <v>3</v>
       </c>
-      <c r="I102" s="8">
+      <c r="I102" s="7">
         <v>8000</v>
       </c>
       <c r="J102" s="5" t="s">
@@ -23488,15 +23483,15 @@
         <v>19</v>
       </c>
       <c r="C103" s="2" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>2198</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>2199</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F103" s="15">
         <v>1490</v>
       </c>
       <c r="G103" s="4" t="s">
@@ -23505,20 +23500,20 @@
       <c r="H103" s="3">
         <v>4</v>
       </c>
-      <c r="I103" s="8">
+      <c r="I103" s="7">
         <v>8000</v>
       </c>
       <c r="J103" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="L103" s="4">
         <v>400</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="N103" s="4">
         <v>6</v>
@@ -23532,10 +23527,10 @@
         <v>386</v>
       </c>
       <c r="C104" s="4" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>2200</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>2201</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>1807</v>
@@ -23549,20 +23544,20 @@
       <c r="H104" s="3">
         <v>1</v>
       </c>
-      <c r="I104" s="8">
+      <c r="I104" s="7">
         <v>100000</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="L104" s="4">
         <v>120</v>
       </c>
       <c r="M104" s="4" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="N104" s="4">
         <v>16</v>
@@ -23576,10 +23571,10 @@
         <v>852</v>
       </c>
       <c r="C105" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>2204</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>2205</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>1814</v>
@@ -23593,20 +23588,20 @@
       <c r="H105" s="3">
         <v>1</v>
       </c>
-      <c r="I105" s="8">
+      <c r="I105" s="7">
         <v>5000</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="L105" s="4">
         <v>90</v>
       </c>
       <c r="M105" s="4" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="N105" s="4">
         <v>1</v>
@@ -23614,21 +23609,21 @@
     </row>
     <row r="106" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B106" s="4" t="s">
         <v>2208</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="C106" s="4" t="s">
         <v>2209</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="D106" s="4" t="s">
         <v>2210</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>2211</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F106" s="7">
+      <c r="F106" s="15">
         <v>10</v>
       </c>
       <c r="G106" s="4" t="s">
@@ -23637,20 +23632,20 @@
       <c r="H106" s="3">
         <v>1</v>
       </c>
-      <c r="I106" s="8">
+      <c r="I106" s="7">
         <v>2500</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="L106" s="4">
         <v>55</v>
       </c>
       <c r="M106" s="4" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="N106" s="4">
         <v>1</v>
@@ -23664,10 +23659,10 @@
         <v>1426</v>
       </c>
       <c r="C107" s="4" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>2214</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>2215</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>1807</v>
@@ -23681,20 +23676,20 @@
       <c r="H107" s="3">
         <v>1</v>
       </c>
-      <c r="I107" s="8">
+      <c r="I107" s="7">
         <v>4000</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="L107" s="4">
         <v>97</v>
       </c>
       <c r="M107" s="4" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="N107" s="4">
         <v>2</v>
@@ -23708,15 +23703,15 @@
         <v>253</v>
       </c>
       <c r="C108" s="4" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>2218</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>2219</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F108" s="15">
         <v>1633</v>
       </c>
       <c r="G108" s="4" t="s">
@@ -23725,20 +23720,20 @@
       <c r="H108" s="3">
         <v>1</v>
       </c>
-      <c r="I108" s="8">
+      <c r="I108" s="7">
         <v>85000</v>
       </c>
       <c r="J108" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="L108" s="4">
         <v>0</v>
       </c>
       <c r="M108" s="4" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="N108" s="4">
         <v>4</v>
@@ -23746,21 +23741,21 @@
     </row>
     <row r="109" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C109" s="2" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>2223</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>2224</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F109" s="7">
+      <c r="F109" s="15">
         <v>4566</v>
       </c>
       <c r="G109" s="4" t="s">
@@ -23769,20 +23764,20 @@
       <c r="H109" s="3">
         <v>3</v>
       </c>
-      <c r="I109" s="8">
+      <c r="I109" s="7">
         <v>4000000</v>
       </c>
       <c r="J109" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="L109" s="4">
         <v>0</v>
       </c>
       <c r="M109" s="4" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="N109" s="4">
         <v>3</v>
@@ -23790,16 +23785,16 @@
     </row>
     <row r="110" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>1103</v>
       </c>
       <c r="C110" s="2" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>2228</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>2229</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>1807</v>
@@ -23820,13 +23815,13 @@
         <v>1809</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="L110" s="4">
         <v>70</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="N110" s="4">
         <v>1</v>
@@ -23834,16 +23829,16 @@
     </row>
     <row r="111" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>177</v>
       </c>
       <c r="C111" s="4" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>2233</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>2234</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>1814</v>
@@ -23857,20 +23852,20 @@
       <c r="H111" s="3">
         <v>2</v>
       </c>
-      <c r="I111" s="8">
+      <c r="I111" s="7">
         <v>250000</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="L111" s="4">
         <v>0</v>
       </c>
       <c r="M111" s="4" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="N111" s="4">
         <v>2</v>
@@ -23884,15 +23879,15 @@
         <v>48</v>
       </c>
       <c r="C112" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>2237</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>2238</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F112" s="7">
+      <c r="F112" s="15">
         <v>4471</v>
       </c>
       <c r="G112" s="4" t="s">
@@ -23901,20 +23896,20 @@
       <c r="H112" s="3">
         <v>3</v>
       </c>
-      <c r="I112" s="8">
+      <c r="I112" s="7">
         <v>4500000</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="L112" s="4">
         <v>0</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="N112" s="4">
         <v>3</v>
@@ -23922,16 +23917,16 @@
     </row>
     <row r="113" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>910</v>
       </c>
       <c r="C113" s="4" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>2241</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>2242</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>1814</v>
@@ -23945,20 +23940,20 @@
       <c r="H113" s="3">
         <v>2</v>
       </c>
-      <c r="I113" s="8">
+      <c r="I113" s="7">
         <v>4000</v>
       </c>
       <c r="J113" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="L113" s="4">
         <v>290</v>
       </c>
       <c r="M113" s="4" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="N113" s="4">
         <v>2</v>
@@ -23966,21 +23961,21 @@
     </row>
     <row r="114" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>910</v>
       </c>
       <c r="C114" s="4" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>2245</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>2246</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F114" s="7">
+      <c r="F114" s="15">
         <v>2119</v>
       </c>
       <c r="G114" s="4" t="s">
@@ -23989,20 +23984,20 @@
       <c r="H114" s="3">
         <v>2</v>
       </c>
-      <c r="I114" s="8">
+      <c r="I114" s="7">
         <v>30000</v>
       </c>
       <c r="J114" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="L114" s="4">
         <v>185</v>
       </c>
       <c r="M114" s="4" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="N114" s="4">
         <v>2</v>
@@ -24016,15 +24011,15 @@
         <v>283</v>
       </c>
       <c r="C115" s="2" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>2247</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>2248</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F115" s="7">
+      <c r="F115" s="15">
         <v>12173</v>
       </c>
       <c r="G115" s="4" t="s">
@@ -24033,20 +24028,20 @@
       <c r="H115" s="3">
         <v>5</v>
       </c>
-      <c r="I115" s="8">
+      <c r="I115" s="7">
         <v>3800</v>
       </c>
       <c r="J115" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="L115" s="4">
         <v>670</v>
       </c>
       <c r="M115" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="N115" s="4">
         <v>5</v>
@@ -24054,21 +24049,21 @@
     </row>
     <row r="116" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>2251</v>
       </c>
-      <c r="B116" s="4" t="s">
-        <v>2209</v>
-      </c>
-      <c r="C116" s="4" t="s">
+      <c r="D116" s="4" t="s">
         <v>2252</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>2253</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F116" s="7">
+      <c r="F116" s="15">
         <v>157</v>
       </c>
       <c r="G116" s="4" t="s">
@@ -24077,20 +24072,20 @@
       <c r="H116" s="3">
         <v>1</v>
       </c>
-      <c r="I116" s="8">
+      <c r="I116" s="7">
         <v>85000</v>
       </c>
       <c r="J116" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="L116" s="4">
         <v>0</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="N116" s="4">
         <v>1</v>
@@ -24098,21 +24093,21 @@
     </row>
     <row r="117" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C117" s="4" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>2255</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>2256</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F117" s="7">
+      <c r="F117" s="15">
         <v>1028</v>
       </c>
       <c r="G117" s="4" t="s">
@@ -24121,20 +24116,20 @@
       <c r="H117" s="3">
         <v>1</v>
       </c>
-      <c r="I117" s="8">
+      <c r="I117" s="7">
         <v>47000</v>
       </c>
       <c r="J117" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L117" s="4">
         <v>0</v>
       </c>
       <c r="M117" s="4" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="N117" s="4">
         <v>66</v>
@@ -24148,10 +24143,10 @@
         <v>420</v>
       </c>
       <c r="C118" s="2" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>2258</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>2259</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>1807</v>
@@ -24165,20 +24160,20 @@
       <c r="H118" s="3">
         <v>1</v>
       </c>
-      <c r="I118" s="8">
+      <c r="I118" s="7">
         <v>230000</v>
       </c>
       <c r="J118" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="L118" s="4">
         <v>0</v>
       </c>
       <c r="M118" s="4" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="N118" s="4">
         <v>2</v>
@@ -24186,21 +24181,21 @@
     </row>
     <row r="119" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>2262</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="2" t="s">
         <v>2263</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="D119" s="2" t="s">
         <v>2264</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>2265</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F119" s="7">
+      <c r="F119" s="15">
         <v>181</v>
       </c>
       <c r="G119" s="2" t="s">
@@ -24209,42 +24204,42 @@
       <c r="H119" s="3">
         <v>1</v>
       </c>
-      <c r="I119" s="10">
+      <c r="I119" s="9">
         <v>28000</v>
       </c>
       <c r="J119" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K119" s="2" t="s">
+        <v>2265</v>
+      </c>
+      <c r="L119" s="8">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="s">
         <v>2266</v>
       </c>
-      <c r="L119" s="9">
-        <v>0</v>
-      </c>
-      <c r="M119" s="2" t="s">
-        <v>2267</v>
-      </c>
-      <c r="N119" s="9">
+      <c r="N119" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C120" s="2" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>2269</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>2270</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F120" s="7">
+      <c r="F120" s="15">
         <v>1128</v>
       </c>
       <c r="G120" s="4" t="s">
@@ -24253,7 +24248,7 @@
       <c r="H120" s="3">
         <v>2</v>
       </c>
-      <c r="I120" s="8">
+      <c r="I120" s="7">
         <v>350000</v>
       </c>
       <c r="J120" s="5" t="s">
@@ -24266,7 +24261,7 @@
         <v>190</v>
       </c>
       <c r="M120" s="4" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="N120" s="4">
         <v>3</v>
@@ -24274,22 +24269,22 @@
     </row>
     <row r="121" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C121" s="4" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>2273</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>2274</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F121" s="3">
-        <v>1883</v>
+        <v>1893</v>
       </c>
       <c r="G121" s="4" t="s">
         <v>1815</v>
@@ -24297,7 +24292,7 @@
       <c r="H121" s="3">
         <v>14</v>
       </c>
-      <c r="I121" s="8">
+      <c r="I121" s="7">
         <v>165000</v>
       </c>
       <c r="J121" s="5" t="s">
@@ -24310,7 +24305,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="4" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="N121" s="4">
         <v>22</v>
@@ -24318,21 +24313,21 @@
     </row>
     <row r="122" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>905</v>
       </c>
       <c r="C122" s="2" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>2276</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>2277</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F122" s="7">
+      <c r="F122" s="15">
         <v>1864</v>
       </c>
       <c r="G122" s="4" t="s">
@@ -24341,20 +24336,20 @@
       <c r="H122" s="3">
         <v>1</v>
       </c>
-      <c r="I122" s="8">
+      <c r="I122" s="7">
         <v>1300000</v>
       </c>
       <c r="J122" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="L122" s="4">
         <v>0</v>
       </c>
       <c r="M122" s="4" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="N122" s="4">
         <v>1</v>
@@ -24362,22 +24357,22 @@
     </row>
     <row r="123" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C123" s="2" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>2281</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>2282</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F123" s="3">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>1836</v>
@@ -24385,7 +24380,7 @@
       <c r="H123" s="3">
         <v>5</v>
       </c>
-      <c r="I123" s="8">
+      <c r="I123" s="7">
         <v>330000</v>
       </c>
       <c r="J123" s="5" t="s">
@@ -24398,7 +24393,7 @@
         <v>240</v>
       </c>
       <c r="M123" s="4" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="N123" s="4">
         <v>33</v>
@@ -24406,22 +24401,22 @@
     </row>
     <row r="124" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C124" s="2" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>2285</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>2286</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F124" s="7">
-        <v>186</v>
+      <c r="F124" s="15">
+        <v>217</v>
       </c>
       <c r="G124" s="4" t="s">
         <v>1815</v>
@@ -24436,13 +24431,13 @@
         <v>1823</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="L124" s="4">
         <v>620</v>
       </c>
       <c r="M124" s="4" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="N124" s="4">
         <v>1</v>
@@ -24450,16 +24445,16 @@
     </row>
     <row r="125" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C125" s="4" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>2289</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>2290</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>1807</v>
@@ -24480,13 +24475,13 @@
         <v>1823</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L125" s="4">
         <v>275</v>
       </c>
       <c r="M125" s="4" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="N125" s="4">
         <v>1</v>
@@ -24494,16 +24489,16 @@
     </row>
     <row r="126" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C126" s="2" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D126" s="4" t="s">
         <v>2293</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>2294</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>1814</v>
@@ -24517,7 +24512,7 @@
       <c r="H126" s="3">
         <v>1</v>
       </c>
-      <c r="I126" s="8">
+      <c r="I126" s="7">
         <v>2300</v>
       </c>
       <c r="J126" s="5" t="s">
@@ -24538,22 +24533,22 @@
     </row>
     <row r="127" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>1842</v>
       </c>
       <c r="C127" s="2" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D127" s="2" t="s">
         <v>2296</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>2297</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F127" s="3">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>1836</v>
@@ -24561,20 +24556,20 @@
       <c r="H127" s="3">
         <v>2</v>
       </c>
-      <c r="I127" s="8">
+      <c r="I127" s="7">
         <v>50000</v>
       </c>
       <c r="J127" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="L127" s="4">
         <v>85</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="N127" s="4">
         <v>2</v>
@@ -24582,22 +24577,22 @@
     </row>
     <row r="128" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C128" s="4" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>2300</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>2301</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F128" s="3">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>1815</v>
@@ -24605,7 +24600,7 @@
       <c r="H128" s="3">
         <v>13</v>
       </c>
-      <c r="I128" s="8">
+      <c r="I128" s="7">
         <v>8000</v>
       </c>
       <c r="J128" s="5" t="s">
@@ -24618,7 +24613,7 @@
         <v>60</v>
       </c>
       <c r="M128" s="4" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="N128" s="4">
         <v>26</v>
@@ -24626,22 +24621,22 @@
     </row>
     <row r="129" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C129" s="4" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>2303</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>2304</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F129" s="7">
-        <v>1600</v>
+      <c r="F129" s="15">
+        <v>855</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>1815</v>
@@ -24656,13 +24651,13 @@
         <v>1823</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L129" s="4">
         <v>185</v>
       </c>
       <c r="M129" s="4" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="N129" s="4">
         <v>2</v>
@@ -24676,10 +24671,10 @@
         <v>42</v>
       </c>
       <c r="C130" s="2" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D130" s="4" t="s">
         <v>2305</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>2306</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>1814</v>
@@ -24693,20 +24688,20 @@
       <c r="H130" s="3">
         <v>5</v>
       </c>
-      <c r="I130" s="8">
+      <c r="I130" s="7">
         <v>18000</v>
       </c>
       <c r="J130" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="L130" s="4">
         <v>25</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="N130" s="4">
         <v>13</v>
@@ -24714,16 +24709,16 @@
     </row>
     <row r="131" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>1103</v>
       </c>
       <c r="C131" s="2" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D131" s="4" t="s">
         <v>2310</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>2311</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>1807</v>
@@ -24744,7 +24739,7 @@
         <v>1809</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="L131" s="4">
         <v>45</v>
@@ -24764,16 +24759,16 @@
         <v>48</v>
       </c>
       <c r="C132" s="4" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D132" s="4" t="s">
         <v>2312</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>2313</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F132" s="7">
-        <v>3219</v>
+      <c r="F132" s="15">
+        <v>2955</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>1815</v>
@@ -24781,20 +24776,20 @@
       <c r="H132" s="3">
         <v>3</v>
       </c>
-      <c r="I132" s="8">
+      <c r="I132" s="7">
         <v>350000</v>
       </c>
       <c r="J132" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="L132" s="4">
         <v>110</v>
       </c>
       <c r="M132" s="4" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="N132" s="4">
         <v>5</v>
@@ -24808,16 +24803,16 @@
         <v>26</v>
       </c>
       <c r="C133" s="2" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>2315</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>2316</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F133" s="3">
-        <v>272</v>
+        <v>123</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>1808</v>
@@ -24825,7 +24820,7 @@
       <c r="H133" s="3">
         <v>1</v>
       </c>
-      <c r="I133" s="8">
+      <c r="I133" s="7">
         <v>14000</v>
       </c>
       <c r="J133" s="5" t="s">
@@ -24838,7 +24833,7 @@
         <v>90</v>
       </c>
       <c r="M133" s="4" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="N133" s="4">
         <v>4</v>
@@ -24851,17 +24846,17 @@
       <c r="B134" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="C134" s="11" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D134" s="2" t="s">
         <v>2318</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>2319</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F134" s="7">
-        <v>2528</v>
+      <c r="F134" s="15">
+        <v>2513</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>1808</v>
@@ -24869,20 +24864,20 @@
       <c r="H134" s="3">
         <v>1</v>
       </c>
-      <c r="I134" s="8">
+      <c r="I134" s="7">
         <v>3000</v>
       </c>
       <c r="J134" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="L134" s="4">
         <v>300</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="N134" s="4">
         <v>4</v>
@@ -24896,16 +24891,16 @@
         <v>48</v>
       </c>
       <c r="C135" s="2" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>2322</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>2323</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F135" s="7">
-        <v>5345</v>
+      <c r="F135" s="15">
+        <v>4150</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>1836</v>
@@ -24913,20 +24908,20 @@
       <c r="H135" s="3">
         <v>1</v>
       </c>
-      <c r="I135" s="8">
+      <c r="I135" s="7">
         <v>900000</v>
       </c>
       <c r="J135" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="L135" s="4">
         <v>0</v>
       </c>
       <c r="M135" s="4" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="N135" s="4">
         <v>1</v>
@@ -24934,22 +24929,22 @@
     </row>
     <row r="136" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B136" s="4" t="s">
         <v>2325</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="C136" s="4" t="s">
         <v>2326</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="D136" s="4" t="s">
         <v>2327</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>2328</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F136" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>1815</v>
@@ -24964,13 +24959,13 @@
         <v>1809</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="L136" s="4">
         <v>690</v>
       </c>
       <c r="M136" s="4" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="N136" s="4">
         <v>2</v>
@@ -24984,16 +24979,16 @@
         <v>636</v>
       </c>
       <c r="C137" s="2" t="s">
+        <v>2329</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>2330</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>2331</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F137" s="3">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>1808</v>
@@ -25001,20 +24996,20 @@
       <c r="H137" s="3">
         <v>3</v>
       </c>
-      <c r="I137" s="8">
+      <c r="I137" s="7">
         <v>1500</v>
       </c>
       <c r="J137" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="L137" s="4">
         <v>185</v>
       </c>
       <c r="M137" s="4" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="N137" s="4">
         <v>1</v>
@@ -25028,16 +25023,16 @@
         <v>1457</v>
       </c>
       <c r="C138" s="2" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>2333</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>2334</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F138" s="3">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>1836</v>
@@ -25045,20 +25040,20 @@
       <c r="H138" s="3">
         <v>1</v>
       </c>
-      <c r="I138" s="8">
+      <c r="I138" s="7">
         <v>100000</v>
       </c>
       <c r="J138" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="L138" s="4">
         <v>160</v>
       </c>
       <c r="M138" s="4" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="N138" s="4">
         <v>4</v>
@@ -25072,16 +25067,16 @@
         <v>26</v>
       </c>
       <c r="C139" s="2" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D139" s="4" t="s">
         <v>2337</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>2338</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F139" s="7">
-        <v>1545</v>
+      <c r="F139" s="15">
+        <v>1559</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>1815</v>
@@ -25089,7 +25084,7 @@
       <c r="H139" s="3">
         <v>21</v>
       </c>
-      <c r="I139" s="8">
+      <c r="I139" s="7">
         <v>1000000</v>
       </c>
       <c r="J139" s="5" t="s">
@@ -25102,7 +25097,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="4" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="N139" s="4">
         <v>31</v>
@@ -25116,16 +25111,16 @@
         <v>32</v>
       </c>
       <c r="C140" s="2" t="s">
+        <v>2339</v>
+      </c>
+      <c r="D140" s="4" t="s">
         <v>2340</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>2341</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F140" s="7">
-        <v>1200</v>
+      <c r="F140" s="15">
+        <v>1209</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>1815</v>
@@ -25133,7 +25128,7 @@
       <c r="H140" s="3">
         <v>21</v>
       </c>
-      <c r="I140" s="8">
+      <c r="I140" s="7">
         <v>1400000</v>
       </c>
       <c r="J140" s="5" t="s">
@@ -25154,16 +25149,16 @@
     </row>
     <row r="141" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C141" s="2" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D141" s="4" t="s">
         <v>2343</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>2344</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>1807</v>
@@ -25177,7 +25172,7 @@
       <c r="H141" s="3">
         <v>2</v>
       </c>
-      <c r="I141" s="8">
+      <c r="I141" s="7">
         <v>13000</v>
       </c>
       <c r="J141" s="5" t="s">
@@ -25198,16 +25193,16 @@
     </row>
     <row r="142" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="6" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C142" s="2" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D142" s="2" t="s">
         <v>2346</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>2347</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>1807</v>
@@ -25221,7 +25216,7 @@
       <c r="H142" s="3">
         <v>1</v>
       </c>
-      <c r="I142" s="8">
+      <c r="I142" s="7">
         <v>3000</v>
       </c>
       <c r="J142" s="5" t="s">
@@ -25234,7 +25229,7 @@
         <v>115</v>
       </c>
       <c r="M142" s="4" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="N142" s="4">
         <v>1</v>
@@ -25242,22 +25237,22 @@
     </row>
     <row r="143" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C143" s="2" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D143" s="2" t="s">
         <v>2350</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>2351</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F143" s="3">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>1815</v>
@@ -25272,7 +25267,7 @@
         <v>1823</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="L143" s="4">
         <v>485</v>
@@ -25286,22 +25281,22 @@
     </row>
     <row r="144" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="6" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C144" s="2" t="s">
+        <v>2353</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>2354</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>2355</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F144" s="3">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>1815</v>
@@ -25309,20 +25304,20 @@
       <c r="H144" s="3">
         <v>1</v>
       </c>
-      <c r="I144" s="8">
+      <c r="I144" s="7">
         <v>5500</v>
       </c>
       <c r="J144" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L144" s="4">
         <v>120</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="N144" s="4">
         <v>1</v>
@@ -25336,16 +25331,16 @@
         <v>91</v>
       </c>
       <c r="C145" s="2" t="s">
+        <v>2356</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>2357</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>2358</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F145" s="3">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>1808</v>
@@ -25353,7 +25348,7 @@
       <c r="H145" s="3">
         <v>1</v>
       </c>
-      <c r="I145" s="8">
+      <c r="I145" s="7">
         <v>9000</v>
       </c>
       <c r="J145" s="5" t="s">
@@ -25366,7 +25361,7 @@
         <v>40</v>
       </c>
       <c r="M145" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="N145" s="4">
         <v>1</v>
@@ -25374,22 +25369,22 @@
     </row>
     <row r="146" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="6" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>1254</v>
       </c>
       <c r="C146" s="4" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D146" s="4" t="s">
         <v>2361</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>2362</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F146" s="3">
-        <v>459</v>
+        <v>369</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>1815</v>
@@ -25397,20 +25392,20 @@
       <c r="H146" s="3">
         <v>4</v>
       </c>
-      <c r="I146" s="8">
+      <c r="I146" s="7">
         <v>18000</v>
       </c>
       <c r="J146" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="L146" s="4">
         <v>0</v>
       </c>
       <c r="M146" s="4" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="N146" s="4">
         <v>93</v>
@@ -25424,16 +25419,16 @@
         <v>420</v>
       </c>
       <c r="C147" s="4" t="s">
+        <v>2364</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>2365</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>2366</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F147" s="7">
-        <v>14650</v>
+      <c r="F147" s="15">
+        <v>11498</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>1815</v>
@@ -25441,20 +25436,20 @@
       <c r="H147" s="3">
         <v>2</v>
       </c>
-      <c r="I147" s="8">
+      <c r="I147" s="7">
         <v>1200000</v>
       </c>
       <c r="J147" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="L147" s="4">
         <v>0</v>
       </c>
       <c r="M147" s="4" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="N147" s="4">
         <v>3</v>
@@ -25468,16 +25463,16 @@
         <v>420</v>
       </c>
       <c r="C148" s="2" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D148" s="4" t="s">
         <v>2369</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>2370</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F148" s="7">
-        <v>12000</v>
+      <c r="F148" s="15">
+        <v>11498</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>1815</v>
@@ -25485,20 +25480,20 @@
       <c r="H148" s="3">
         <v>2</v>
       </c>
-      <c r="I148" s="8">
+      <c r="I148" s="7">
         <v>4500000</v>
       </c>
       <c r="J148" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K148" s="4" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="L148" s="4">
         <v>0</v>
       </c>
       <c r="M148" s="4" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="N148" s="4">
         <v>39</v>
@@ -25506,22 +25501,22 @@
     </row>
     <row r="149" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C149" s="2" t="s">
+        <v>2372</v>
+      </c>
+      <c r="D149" s="2" t="s">
         <v>2373</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>2374</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F149" s="7">
-        <v>2050</v>
+      <c r="F149" s="15">
+        <v>2030</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>1815</v>
@@ -25529,20 +25524,20 @@
       <c r="H149" s="3">
         <v>2</v>
       </c>
-      <c r="I149" s="8">
+      <c r="I149" s="7">
         <v>2500</v>
       </c>
       <c r="J149" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K149" s="4" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="L149" s="4">
         <v>360</v>
       </c>
       <c r="M149" s="4" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="N149" s="4">
         <v>3</v>
@@ -25556,16 +25551,16 @@
         <v>386</v>
       </c>
       <c r="C150" s="2" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>2376</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>2377</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F150" s="3">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>1836</v>
@@ -25573,20 +25568,20 @@
       <c r="H150" s="3">
         <v>1</v>
       </c>
-      <c r="I150" s="8">
+      <c r="I150" s="7">
         <v>800000</v>
       </c>
       <c r="J150" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="L150" s="4">
         <v>0</v>
       </c>
       <c r="M150" s="4" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="N150" s="4">
         <v>63</v>
@@ -25594,22 +25589,22 @@
     </row>
     <row r="151" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>910</v>
       </c>
       <c r="C151" s="4" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>2379</v>
-      </c>
-      <c r="D151" s="4" t="s">
-        <v>2380</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F151" s="3">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>1815</v>
@@ -25617,20 +25612,20 @@
       <c r="H151" s="3">
         <v>2</v>
       </c>
-      <c r="I151" s="8">
+      <c r="I151" s="7">
         <v>18000</v>
       </c>
       <c r="J151" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K151" s="4" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="L151" s="4">
         <v>220</v>
       </c>
       <c r="M151" s="4" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="N151" s="4">
         <v>2</v>
@@ -25644,16 +25639,16 @@
         <v>322</v>
       </c>
       <c r="C152" s="2" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D152" s="4" t="s">
         <v>2382</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>2383</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F152" s="3">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>1815</v>
@@ -25661,20 +25656,20 @@
       <c r="H152" s="3">
         <v>3</v>
       </c>
-      <c r="I152" s="8">
+      <c r="I152" s="7">
         <v>180000</v>
       </c>
       <c r="J152" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="L152" s="4">
         <v>130</v>
       </c>
       <c r="M152" s="4" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="N152" s="4">
         <v>80</v>
@@ -25688,16 +25683,16 @@
         <v>1254</v>
       </c>
       <c r="C153" s="2" t="s">
+        <v>2385</v>
+      </c>
+      <c r="D153" s="4" t="s">
         <v>2386</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>2387</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F153" s="3">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="G153" s="4" t="s">
         <v>1815</v>
@@ -25705,20 +25700,20 @@
       <c r="H153" s="3">
         <v>4</v>
       </c>
-      <c r="I153" s="8">
+      <c r="I153" s="7">
         <v>36000</v>
       </c>
       <c r="J153" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="L153" s="4">
         <v>0</v>
       </c>
       <c r="M153" s="4" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="N153" s="4">
         <v>59</v>
@@ -25732,16 +25727,16 @@
         <v>26</v>
       </c>
       <c r="C154" s="2" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D154" s="4" t="s">
         <v>2388</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>2389</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F154" s="7">
-        <v>13790</v>
+      <c r="F154" s="15">
+        <v>8759</v>
       </c>
       <c r="G154" s="4" t="s">
         <v>1808</v>
@@ -25749,20 +25744,20 @@
       <c r="H154" s="3">
         <v>26</v>
       </c>
-      <c r="I154" s="8">
+      <c r="I154" s="7">
         <v>3200000</v>
       </c>
       <c r="J154" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K154" s="4" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="L154" s="4">
         <v>0</v>
       </c>
       <c r="M154" s="4" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="N154" s="4">
         <v>27</v>
@@ -25770,22 +25765,22 @@
     </row>
     <row r="155" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C155" s="2" t="s">
+        <v>2392</v>
+      </c>
+      <c r="D155" s="2" t="s">
         <v>2393</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>2394</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F155" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>1808</v>
@@ -25793,20 +25788,20 @@
       <c r="H155" s="3">
         <v>1</v>
       </c>
-      <c r="I155" s="8">
+      <c r="I155" s="7">
         <v>5500</v>
       </c>
       <c r="J155" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="L155" s="4">
         <v>70</v>
       </c>
       <c r="M155" s="4" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="N155" s="4">
         <v>1</v>
@@ -25814,21 +25809,21 @@
     </row>
     <row r="156" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>2397</v>
       </c>
-      <c r="B156" s="4" t="s">
-        <v>2209</v>
-      </c>
-      <c r="C156" s="4" t="s">
+      <c r="D156" s="4" t="s">
         <v>2398</v>
-      </c>
-      <c r="D156" s="4" t="s">
-        <v>2399</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F156" s="7">
+      <c r="F156" s="15">
         <v>38</v>
       </c>
       <c r="G156" s="4" t="s">
@@ -25837,20 +25832,20 @@
       <c r="H156" s="3">
         <v>1</v>
       </c>
-      <c r="I156" s="8">
+      <c r="I156" s="7">
         <v>7000</v>
       </c>
       <c r="J156" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="L156" s="4">
         <v>50</v>
       </c>
       <c r="M156" s="4" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="N156" s="4">
         <v>1</v>
@@ -25858,22 +25853,22 @@
     </row>
     <row r="157" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C157" s="2" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D157" s="4" t="s">
         <v>2401</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>2402</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F157" s="3" t="s">
-        <v>2403</v>
+      <c r="F157" s="3">
+        <v>5740</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>1808</v>
@@ -25881,7 +25876,7 @@
       <c r="H157" s="3">
         <v>11</v>
       </c>
-      <c r="I157" s="8">
+      <c r="I157" s="7">
         <v>180000</v>
       </c>
       <c r="J157" s="5" t="s">
@@ -25894,7 +25889,7 @@
         <v>0</v>
       </c>
       <c r="M157" s="4" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="N157" s="4">
         <v>6</v>
@@ -25908,16 +25903,16 @@
         <v>26</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F158" s="7">
-        <v>17293</v>
+      <c r="F158" s="15">
+        <v>7232</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>1815</v>
@@ -25925,14 +25920,14 @@
       <c r="H158" s="3">
         <v>7</v>
       </c>
-      <c r="I158" s="8">
+      <c r="I158" s="7">
         <v>6000</v>
       </c>
       <c r="J158" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K158" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L158" s="4">
         <v>350</v>
@@ -25952,16 +25947,16 @@
         <v>247</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F159" s="3">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>1815</v>
@@ -25969,7 +25964,7 @@
       <c r="H159" s="3">
         <v>1</v>
       </c>
-      <c r="I159" s="8">
+      <c r="I159" s="7">
         <v>7000</v>
       </c>
       <c r="J159" s="5" t="s">
@@ -25990,22 +25985,22 @@
     </row>
     <row r="160" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="6" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>2408</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>2409</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="D160" s="4" t="s">
         <v>2410</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>2411</v>
-      </c>
-      <c r="D160" s="4" t="s">
-        <v>2412</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F160" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>1815</v>
@@ -26013,20 +26008,20 @@
       <c r="H160" s="3">
         <v>2</v>
       </c>
-      <c r="I160" s="8">
+      <c r="I160" s="7">
         <v>11000</v>
       </c>
       <c r="J160" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="L160" s="4">
         <v>0</v>
       </c>
       <c r="M160" s="4" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="N160" s="4">
         <v>2</v>
@@ -26034,22 +26029,22 @@
     </row>
     <row r="161" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F161" s="3">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>1815</v>
@@ -26064,7 +26059,7 @@
         <v>1823</v>
       </c>
       <c r="K161" s="4" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="L161" s="4">
         <v>710</v>
@@ -26084,16 +26079,16 @@
         <v>42</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F162" s="7">
-        <v>2512</v>
+      <c r="F162" s="15">
+        <v>2520</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>1836</v>
@@ -26101,7 +26096,7 @@
       <c r="H162" s="3">
         <v>23</v>
       </c>
-      <c r="I162" s="8">
+      <c r="I162" s="7">
         <v>870000</v>
       </c>
       <c r="J162" s="5" t="s">
@@ -26114,7 +26109,7 @@
         <v>0</v>
       </c>
       <c r="M162" s="4" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="N162" s="4">
         <v>40</v>
@@ -26128,16 +26123,16 @@
         <v>253</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F163" s="7">
-        <v>1401</v>
+      <c r="F163" s="15">
+        <v>1405</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>1808</v>
@@ -26145,20 +26140,20 @@
       <c r="H163" s="3">
         <v>2</v>
       </c>
-      <c r="I163" s="8">
+      <c r="I163" s="7">
         <v>120000</v>
       </c>
       <c r="J163" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="L163" s="4">
         <v>0</v>
       </c>
       <c r="M163" s="4" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="N163" s="4">
         <v>1</v>
@@ -26166,22 +26161,22 @@
     </row>
     <row r="164" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="6" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>1233</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F164" s="3">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>1808</v>
@@ -26189,20 +26184,20 @@
       <c r="H164" s="3">
         <v>1</v>
       </c>
-      <c r="I164" s="8">
+      <c r="I164" s="7">
         <v>120000</v>
       </c>
       <c r="J164" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K164" s="4" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="L164" s="4">
         <v>87</v>
       </c>
       <c r="M164" s="4" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="N164" s="4">
         <v>39</v>
@@ -26210,43 +26205,43 @@
     </row>
     <row r="165" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F165" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>1815</v>
       </c>
-      <c r="H165" s="11">
+      <c r="H165" s="10">
         <v>1</v>
       </c>
-      <c r="I165" s="8">
+      <c r="I165" s="7">
         <v>2000</v>
       </c>
       <c r="J165" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K165" s="4" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="L165" s="4">
         <v>575</v>
       </c>
       <c r="M165" s="4" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="N165" s="4">
         <v>1</v>
@@ -26260,16 +26255,16 @@
         <v>732</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F166" s="7">
-        <v>2675</v>
+      <c r="F166" s="15">
+        <v>2701</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>1808</v>
@@ -26277,20 +26272,20 @@
       <c r="H166" s="3">
         <v>1</v>
       </c>
-      <c r="I166" s="8">
+      <c r="I166" s="7">
         <v>33000</v>
       </c>
       <c r="J166" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K166" s="4" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="L166" s="4">
         <v>245</v>
       </c>
       <c r="M166" s="4" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="N166" s="4">
         <v>1</v>
@@ -26304,16 +26299,16 @@
         <v>32</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F167" s="3">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>1815</v>
@@ -26321,7 +26316,7 @@
       <c r="H167" s="3">
         <v>3</v>
       </c>
-      <c r="I167" s="8">
+      <c r="I167" s="7">
         <v>50000</v>
       </c>
       <c r="J167" s="5" t="s">
@@ -26334,7 +26329,7 @@
         <v>60</v>
       </c>
       <c r="M167" s="4" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="N167" s="4">
         <v>13</v>
@@ -26342,22 +26337,22 @@
     </row>
     <row r="168" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="6" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>1103</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F168" s="3">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>1815</v>
@@ -26392,16 +26387,16 @@
         <v>283</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F169" s="3">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>1808</v>
@@ -26409,20 +26404,20 @@
       <c r="H169" s="3">
         <v>1</v>
       </c>
-      <c r="I169" s="8">
+      <c r="I169" s="7">
         <v>4500</v>
       </c>
       <c r="J169" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K169" s="4" t="s">
-        <v>2443</v>
-      </c>
-      <c r="L169" s="8">
+        <v>2441</v>
+      </c>
+      <c r="L169" s="7">
         <v>1910</v>
       </c>
       <c r="M169" s="4" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="N169" s="4">
         <v>1</v>
@@ -26430,22 +26425,22 @@
     </row>
     <row r="170" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="6" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F170" s="3">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>1808</v>
@@ -26466,7 +26461,7 @@
         <v>250</v>
       </c>
       <c r="M170" s="4" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="N170" s="4">
         <v>1</v>
@@ -26480,16 +26475,16 @@
         <v>415</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F171" s="3">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>1815</v>
@@ -26497,20 +26492,20 @@
       <c r="H171" s="3">
         <v>1</v>
       </c>
-      <c r="I171" s="8">
+      <c r="I171" s="7">
         <v>7000</v>
       </c>
       <c r="J171" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K171" s="4" t="s">
-        <v>2451</v>
-      </c>
-      <c r="L171" s="8">
+        <v>2449</v>
+      </c>
+      <c r="L171" s="7">
         <v>0</v>
       </c>
       <c r="M171" s="4" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
       <c r="N171" s="4">
         <v>1</v>
@@ -26518,22 +26513,22 @@
     </row>
     <row r="172" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F172" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>1815</v>
@@ -26541,20 +26536,20 @@
       <c r="H172" s="3">
         <v>1</v>
       </c>
-      <c r="I172" s="8">
+      <c r="I172" s="7">
         <v>8600</v>
       </c>
       <c r="J172" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L172" s="4">
         <v>110</v>
       </c>
       <c r="M172" s="4" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="N172" s="4">
         <v>1</v>
@@ -26568,16 +26563,16 @@
         <v>528</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F173" s="3">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>1808</v>
@@ -26585,14 +26580,14 @@
       <c r="H173" s="3">
         <v>1</v>
       </c>
-      <c r="I173" s="8">
+      <c r="I173" s="7">
         <v>1000</v>
       </c>
       <c r="J173" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="L173" s="4">
         <v>310</v>
@@ -26612,16 +26607,16 @@
         <v>48</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F174" s="3">
-        <v>813</v>
+        <v>556</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>1815</v>
@@ -26629,20 +26624,20 @@
       <c r="H174" s="3">
         <v>2</v>
       </c>
-      <c r="I174" s="8">
+      <c r="I174" s="7">
         <v>140000</v>
       </c>
       <c r="J174" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K174" s="4" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="L174" s="4">
         <v>250</v>
       </c>
       <c r="M174" s="4" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="N174" s="4">
         <v>2</v>
@@ -26650,22 +26645,22 @@
     </row>
     <row r="175" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>1076</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F175" s="3">
-        <v>779</v>
+        <v>792</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>1808</v>
@@ -26673,20 +26668,20 @@
       <c r="H175" s="3">
         <v>1</v>
       </c>
-      <c r="I175" s="8">
+      <c r="I175" s="7">
         <v>35000</v>
       </c>
       <c r="J175" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K175" s="4" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="L175" s="4">
         <v>195</v>
       </c>
       <c r="M175" s="4" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="N175" s="4">
         <v>1</v>
@@ -26694,22 +26689,22 @@
     </row>
     <row r="176" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="6" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>910</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F176" s="7">
-        <v>3955</v>
+      <c r="F176" s="15">
+        <v>3959</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>1815</v>
@@ -26717,20 +26712,20 @@
       <c r="H176" s="3">
         <v>3</v>
       </c>
-      <c r="I176" s="8">
+      <c r="I176" s="7">
         <v>40000</v>
       </c>
       <c r="J176" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K176" s="4" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="L176" s="4">
         <v>300</v>
       </c>
       <c r="M176" s="4" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="N176" s="4">
         <v>4</v>
@@ -26744,16 +26739,16 @@
         <v>26</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F177" s="7">
-        <v>4640</v>
+      <c r="F177" s="15">
+        <v>4593</v>
       </c>
       <c r="G177" s="4" t="s">
         <v>1815</v>
@@ -26770,11 +26765,11 @@
       <c r="K177" s="4" t="s">
         <v>1816</v>
       </c>
-      <c r="L177" s="8">
+      <c r="L177" s="7">
         <v>1085</v>
       </c>
       <c r="M177" s="4" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="N177" s="4">
         <v>21</v>
@@ -26788,10 +26783,10 @@
         <v>177</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>1814</v>
@@ -26805,14 +26800,14 @@
       <c r="H178" s="3">
         <v>3</v>
       </c>
-      <c r="I178" s="8">
+      <c r="I178" s="7">
         <v>135000</v>
       </c>
       <c r="J178" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K178" s="4" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="L178" s="4">
         <v>0</v>
@@ -26826,22 +26821,22 @@
     </row>
     <row r="179" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F179" s="3">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>1815</v>
@@ -26856,9 +26851,9 @@
         <v>1823</v>
       </c>
       <c r="K179" s="4" t="s">
-        <v>2176</v>
-      </c>
-      <c r="L179" s="8">
+        <v>2175</v>
+      </c>
+      <c r="L179" s="7">
         <v>1420</v>
       </c>
       <c r="M179" s="4" t="s">
@@ -26876,16 +26871,16 @@
         <v>283</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F180" s="3" t="s">
-        <v>2482</v>
+      <c r="F180" s="15">
+        <v>1467</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>1808</v>
@@ -26893,20 +26888,20 @@
       <c r="H180" s="3">
         <v>2</v>
       </c>
-      <c r="I180" s="8">
+      <c r="I180" s="7">
         <v>23000</v>
       </c>
       <c r="J180" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K180" s="4" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="L180" s="4">
         <v>360</v>
       </c>
       <c r="M180" s="4" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="N180" s="4">
         <v>3</v>
@@ -26920,16 +26915,16 @@
         <v>32</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>2483</v>
+        <v>2480</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>2484</v>
+        <v>2481</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F181" s="7">
-        <v>18800</v>
+      <c r="F181" s="15">
+        <v>18372</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>1815</v>
@@ -26937,7 +26932,7 @@
       <c r="H181" s="3">
         <v>5</v>
       </c>
-      <c r="I181" s="8">
+      <c r="I181" s="7">
         <v>3700000</v>
       </c>
       <c r="J181" s="5" t="s">
@@ -26950,7 +26945,7 @@
         <v>0</v>
       </c>
       <c r="M181" s="4" t="s">
-        <v>2485</v>
+        <v>2482</v>
       </c>
       <c r="N181" s="4">
         <v>28</v>
@@ -26958,22 +26953,22 @@
     </row>
     <row r="182" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="6" t="s">
-        <v>2486</v>
+        <v>2483</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>2487</v>
+        <v>2484</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>2488</v>
+        <v>2485</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F182" s="3">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>1815</v>
@@ -26988,7 +26983,7 @@
         <v>1823</v>
       </c>
       <c r="K182" s="4" t="s">
-        <v>2489</v>
+        <v>2486</v>
       </c>
       <c r="L182" s="4">
         <v>300</v>
@@ -27008,16 +27003,16 @@
         <v>48</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>2490</v>
+        <v>2487</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>2491</v>
+        <v>2488</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F183" s="7">
-        <v>4030</v>
+      <c r="F183" s="15">
+        <v>3847</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>1836</v>
@@ -27025,20 +27020,20 @@
       <c r="H183" s="3">
         <v>2</v>
       </c>
-      <c r="I183" s="8">
+      <c r="I183" s="7">
         <v>45000</v>
       </c>
       <c r="J183" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K183" s="4" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="L183" s="4">
         <v>180</v>
       </c>
       <c r="M183" s="4" t="s">
-        <v>2492</v>
+        <v>2489</v>
       </c>
       <c r="N183" s="4">
         <v>38</v>
@@ -27046,16 +27041,16 @@
     </row>
     <row r="184" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="6" t="s">
-        <v>2493</v>
+        <v>2490</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>2494</v>
+        <v>2491</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>2495</v>
+        <v>2492</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>1807</v>
@@ -27076,13 +27071,13 @@
         <v>1809</v>
       </c>
       <c r="K184" s="4" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="L184" s="4">
         <v>40</v>
       </c>
       <c r="M184" s="4" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="N184" s="4">
         <v>1</v>
@@ -27096,16 +27091,16 @@
         <v>48</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>2496</v>
+        <v>2493</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>2497</v>
+        <v>2494</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F185" s="7">
-        <v>1754</v>
+      <c r="F185" s="15">
+        <v>1750</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>1836</v>
@@ -27113,20 +27108,20 @@
       <c r="H185" s="3">
         <v>1</v>
       </c>
-      <c r="I185" s="8">
+      <c r="I185" s="7">
         <v>100000</v>
       </c>
       <c r="J185" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K185" s="4" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="L185" s="4">
         <v>300</v>
       </c>
       <c r="M185" s="4" t="s">
-        <v>2498</v>
+        <v>2495</v>
       </c>
       <c r="N185" s="4">
         <v>11</v>
@@ -27134,22 +27129,22 @@
     </row>
     <row r="186" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="6" t="s">
-        <v>2499</v>
+        <v>2496</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>2500</v>
+        <v>2497</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>2501</v>
+        <v>2498</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F186" s="3">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>1815</v>
@@ -27164,13 +27159,13 @@
         <v>1823</v>
       </c>
       <c r="K186" s="4" t="s">
-        <v>2489</v>
+        <v>2486</v>
       </c>
       <c r="L186" s="4">
         <v>705</v>
       </c>
       <c r="M186" s="4" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="N186" s="4">
         <v>1</v>
@@ -27184,16 +27179,16 @@
         <v>464</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>2502</v>
+        <v>2499</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>2503</v>
+        <v>2500</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F187" s="7">
-        <v>1262</v>
+      <c r="F187" s="15">
+        <v>1253</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>1836</v>
@@ -27201,7 +27196,7 @@
       <c r="H187" s="3">
         <v>1</v>
       </c>
-      <c r="I187" s="8">
+      <c r="I187" s="7">
         <v>240000</v>
       </c>
       <c r="J187" s="5" t="s">
@@ -27214,7 +27209,7 @@
         <v>0</v>
       </c>
       <c r="M187" s="4" t="s">
-        <v>2504</v>
+        <v>2501</v>
       </c>
       <c r="N187" s="4">
         <v>1</v>
@@ -27228,16 +27223,16 @@
         <v>1539</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>2505</v>
+        <v>2502</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F188" s="7">
-        <v>1749</v>
+      <c r="F188" s="15">
+        <v>1705</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>1815</v>
@@ -27252,13 +27247,13 @@
         <v>1809</v>
       </c>
       <c r="K188" s="4" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="L188" s="4">
         <v>240</v>
       </c>
       <c r="M188" s="4" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="N188" s="4">
         <v>10</v>
@@ -27266,22 +27261,22 @@
     </row>
     <row r="189" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>2511</v>
+        <v>2508</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F189" s="7">
-        <v>15448</v>
+      <c r="F189" s="15">
+        <v>14510</v>
       </c>
       <c r="G189" s="4" t="s">
         <v>1836</v>
@@ -27289,20 +27284,20 @@
       <c r="H189" s="3">
         <v>1</v>
       </c>
-      <c r="I189" s="8">
+      <c r="I189" s="7">
         <v>1500000</v>
       </c>
       <c r="J189" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K189" s="4" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="L189" s="4">
         <v>215</v>
       </c>
       <c r="M189" s="4" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="N189" s="4">
         <v>2</v>
@@ -27310,21 +27305,21 @@
     </row>
     <row r="190" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="6" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>2510</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D190" s="4" t="s">
         <v>2512</v>
-      </c>
-      <c r="B190" s="4" t="s">
-        <v>2513</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>2514</v>
-      </c>
-      <c r="D190" s="4" t="s">
-        <v>2515</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F190" s="7">
+      <c r="F190" s="15">
         <v>1045</v>
       </c>
       <c r="G190" s="4" t="s">
@@ -27333,20 +27328,20 @@
       <c r="H190" s="3">
         <v>3</v>
       </c>
-      <c r="I190" s="8">
+      <c r="I190" s="7">
         <v>200000</v>
       </c>
       <c r="J190" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K190" s="4" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="L190" s="4">
         <v>0</v>
       </c>
       <c r="M190" s="4" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="N190" s="4">
         <v>6</v>
@@ -27354,22 +27349,22 @@
     </row>
     <row r="191" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F191" s="7">
-        <v>444</v>
+      <c r="F191" s="15">
+        <v>447</v>
       </c>
       <c r="G191" s="4" t="s">
         <v>1815</v>
@@ -27377,7 +27372,7 @@
       <c r="H191" s="3">
         <v>1</v>
       </c>
-      <c r="I191" s="8">
+      <c r="I191" s="7">
         <v>30000</v>
       </c>
       <c r="J191" s="5" t="s">
@@ -27390,7 +27385,7 @@
         <v>120</v>
       </c>
       <c r="M191" s="4" t="s">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="N191" s="4">
         <v>1</v>
@@ -27398,22 +27393,22 @@
     </row>
     <row r="192" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="6" t="s">
-        <v>2521</v>
+        <v>2518</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>2522</v>
+        <v>2519</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F192" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G192" s="4" t="s">
         <v>1815</v>
@@ -27428,13 +27423,13 @@
         <v>1809</v>
       </c>
       <c r="K192" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L192" s="4">
         <v>140</v>
       </c>
       <c r="M192" s="4" t="s">
-        <v>2524</v>
+        <v>2521</v>
       </c>
       <c r="N192" s="4">
         <v>6</v>
@@ -27442,22 +27437,22 @@
     </row>
     <row r="193" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6" t="s">
-        <v>2525</v>
+        <v>2522</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>365</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>2526</v>
+        <v>2523</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>2527</v>
+        <v>2524</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F193" s="3">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>1815</v>
@@ -27465,20 +27460,20 @@
       <c r="H193" s="3">
         <v>3</v>
       </c>
-      <c r="I193" s="8">
+      <c r="I193" s="7">
         <v>20000</v>
       </c>
       <c r="J193" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K193" s="4" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="L193" s="4">
         <v>220</v>
       </c>
       <c r="M193" s="4" t="s">
-        <v>2529</v>
+        <v>2526</v>
       </c>
       <c r="N193" s="4">
         <v>1</v>
@@ -27492,10 +27487,10 @@
         <v>177</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>2530</v>
+        <v>2527</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>2531</v>
+        <v>2528</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>1814</v>
@@ -27509,14 +27504,14 @@
       <c r="H194" s="3">
         <v>1</v>
       </c>
-      <c r="I194" s="8">
+      <c r="I194" s="7">
         <v>53000</v>
       </c>
       <c r="J194" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K194" s="4" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="L194" s="4">
         <v>175</v>
@@ -27536,16 +27531,16 @@
         <v>69</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>2533</v>
+        <v>2530</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F195" s="3">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>1815</v>
@@ -27553,7 +27548,7 @@
       <c r="H195" s="3">
         <v>4</v>
       </c>
-      <c r="I195" s="8">
+      <c r="I195" s="7">
         <v>1200</v>
       </c>
       <c r="J195" s="5" t="s">
@@ -27566,7 +27561,7 @@
         <v>65</v>
       </c>
       <c r="M195" s="4" t="s">
-        <v>2534</v>
+        <v>2531</v>
       </c>
       <c r="N195" s="4">
         <v>1</v>
@@ -27574,16 +27569,16 @@
     </row>
     <row r="196" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="6" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>1180</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>2536</v>
+        <v>2533</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>1807</v>
@@ -27597,7 +27592,7 @@
       <c r="H196" s="3">
         <v>1</v>
       </c>
-      <c r="I196" s="8">
+      <c r="I196" s="7">
         <v>2500</v>
       </c>
       <c r="J196" s="5" t="s">
@@ -27610,7 +27605,7 @@
         <v>0</v>
       </c>
       <c r="M196" s="4" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="N196" s="4">
         <v>1</v>
@@ -27618,22 +27613,22 @@
     </row>
     <row r="197" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>2536</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D197" s="4" t="s">
         <v>2538</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>2539</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>2540</v>
-      </c>
-      <c r="D197" s="4" t="s">
-        <v>2541</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F197" s="3">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>1808</v>
@@ -27641,20 +27636,20 @@
       <c r="H197" s="3">
         <v>2</v>
       </c>
-      <c r="I197" s="8">
+      <c r="I197" s="7">
         <v>60000</v>
       </c>
       <c r="J197" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K197" s="4" t="s">
-        <v>2542</v>
+        <v>2539</v>
       </c>
       <c r="L197" s="4">
         <v>0</v>
       </c>
       <c r="M197" s="4" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
       <c r="N197" s="4">
         <v>12</v>
@@ -27662,16 +27657,16 @@
     </row>
     <row r="198" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="6" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>1814</v>
@@ -27706,22 +27701,22 @@
     </row>
     <row r="199" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6" t="s">
-        <v>2547</v>
+        <v>2544</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F199" s="3">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G199" s="4" t="s">
         <v>1815</v>
@@ -27729,7 +27724,7 @@
       <c r="H199" s="3">
         <v>3</v>
       </c>
-      <c r="I199" s="8">
+      <c r="I199" s="7">
         <v>24000</v>
       </c>
       <c r="J199" s="5" t="s">
@@ -27753,19 +27748,19 @@
         <v>1750</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>2539</v>
+        <v>2536</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>2550</v>
+        <v>2547</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F200" s="7">
-        <v>4768</v>
+      <c r="F200" s="15">
+        <v>4859</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>1808</v>
@@ -27773,20 +27768,20 @@
       <c r="H200" s="3">
         <v>22</v>
       </c>
-      <c r="I200" s="8">
+      <c r="I200" s="7">
         <v>1300000</v>
       </c>
       <c r="J200" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K200" s="4" t="s">
-        <v>2542</v>
+        <v>2539</v>
       </c>
       <c r="L200" s="4">
         <v>0</v>
       </c>
       <c r="M200" s="4" t="s">
-        <v>2552</v>
+        <v>2549</v>
       </c>
       <c r="N200" s="4">
         <v>38</v>
@@ -27794,16 +27789,16 @@
     </row>
     <row r="201" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="6" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>2555</v>
+        <v>2552</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>1814</v>
@@ -27817,20 +27812,20 @@
       <c r="H201" s="3">
         <v>1</v>
       </c>
-      <c r="I201" s="8">
+      <c r="I201" s="7">
         <v>2200</v>
       </c>
       <c r="J201" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K201" s="4" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="L201" s="4">
         <v>645</v>
       </c>
       <c r="M201" s="4" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="N201" s="4">
         <v>1</v>
@@ -27844,16 +27839,16 @@
         <v>26</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>2556</v>
+        <v>2553</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>2557</v>
+        <v>2554</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F202" s="3">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>1815</v>
@@ -27861,20 +27856,20 @@
       <c r="H202" s="3">
         <v>1</v>
       </c>
-      <c r="I202" s="8">
+      <c r="I202" s="7">
         <v>55000</v>
       </c>
       <c r="J202" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K202" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L202" s="4">
         <v>0</v>
       </c>
       <c r="M202" s="4" t="s">
-        <v>2524</v>
+        <v>2521</v>
       </c>
       <c r="N202" s="4">
         <v>9</v>
@@ -27882,22 +27877,22 @@
     </row>
     <row r="203" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="6" t="s">
-        <v>2558</v>
+        <v>2555</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>2560</v>
+        <v>2557</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F203" s="3">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G203" s="4" t="s">
         <v>1815</v>
@@ -27912,13 +27907,13 @@
         <v>1809</v>
       </c>
       <c r="K203" s="4" t="s">
-        <v>2516</v>
-      </c>
-      <c r="L203" s="8">
+        <v>2513</v>
+      </c>
+      <c r="L203" s="7">
         <v>1455</v>
       </c>
       <c r="M203" s="4" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="N203" s="4">
         <v>1</v>
@@ -27926,22 +27921,22 @@
     </row>
     <row r="204" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="6" t="s">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F204" s="7">
-        <v>1776</v>
+      <c r="F204" s="15">
+        <v>1759</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>1815</v>
@@ -27956,13 +27951,13 @@
         <v>1809</v>
       </c>
       <c r="K204" s="4" t="s">
-        <v>2176</v>
-      </c>
-      <c r="L204" s="8">
+        <v>2175</v>
+      </c>
+      <c r="L204" s="7">
         <v>1415</v>
       </c>
       <c r="M204" s="4" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="N204" s="4">
         <v>1</v>
@@ -27970,22 +27965,22 @@
     </row>
     <row r="205" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6" t="s">
-        <v>2564</v>
+        <v>2561</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>2565</v>
+        <v>2562</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>2566</v>
+        <v>2563</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F205" s="7">
-        <v>2720</v>
+      <c r="F205" s="15">
+        <v>2698</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>1815</v>
@@ -27993,20 +27988,20 @@
       <c r="H205" s="3">
         <v>1</v>
       </c>
-      <c r="I205" s="8">
+      <c r="I205" s="7">
         <v>4250</v>
       </c>
       <c r="J205" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K205" s="4" t="s">
-        <v>2176</v>
-      </c>
-      <c r="L205" s="8">
+        <v>2175</v>
+      </c>
+      <c r="L205" s="7">
         <v>1310</v>
       </c>
       <c r="M205" s="4" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="N205" s="4">
         <v>1</v>
@@ -28014,22 +28009,22 @@
     </row>
     <row r="206" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="6" t="s">
-        <v>2567</v>
+        <v>2564</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>494</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>2569</v>
+        <v>2566</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F206" s="7">
-        <v>1125</v>
+      <c r="F206" s="15">
+        <v>1133</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>1815</v>
@@ -28037,20 +28032,20 @@
       <c r="H206" s="3">
         <v>3</v>
       </c>
-      <c r="I206" s="8">
+      <c r="I206" s="7">
         <v>150000</v>
       </c>
       <c r="J206" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K206" s="4" t="s">
-        <v>2570</v>
+        <v>2567</v>
       </c>
       <c r="L206" s="4">
         <v>0</v>
       </c>
       <c r="M206" s="4" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="N206" s="4">
         <v>3</v>
@@ -28064,16 +28059,16 @@
         <v>365</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>2572</v>
+        <v>2569</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>2573</v>
+        <v>2570</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F207" s="7">
-        <v>5560</v>
+      <c r="F207" s="15">
+        <v>5816</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>1815</v>
@@ -28081,20 +28076,20 @@
       <c r="H207" s="3">
         <v>3</v>
       </c>
-      <c r="I207" s="8">
+      <c r="I207" s="7">
         <v>130000</v>
       </c>
       <c r="J207" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K207" s="4" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="L207" s="4">
         <v>195</v>
       </c>
       <c r="M207" s="4" t="s">
-        <v>2529</v>
+        <v>2526</v>
       </c>
       <c r="N207" s="4">
         <v>92</v>
@@ -28102,21 +28097,21 @@
     </row>
     <row r="208" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="6" t="s">
-        <v>2574</v>
+        <v>2571</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>2576</v>
+        <v>2573</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F208" s="7">
+      <c r="F208" s="15">
         <v>135</v>
       </c>
       <c r="G208" s="4" t="s">
@@ -28125,20 +28120,20 @@
       <c r="H208" s="3">
         <v>1</v>
       </c>
-      <c r="I208" s="8">
+      <c r="I208" s="7">
         <v>8000</v>
       </c>
       <c r="J208" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K208" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="L208" s="4">
         <v>70</v>
       </c>
       <c r="M208" s="4" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="N208" s="4">
         <v>1</v>
@@ -28152,16 +28147,16 @@
         <v>365</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>2577</v>
+        <v>2574</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>2578</v>
+        <v>2575</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="F209" s="7">
-        <v>10389</v>
+      <c r="F209" s="15">
+        <v>10691</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>1815</v>
@@ -28169,20 +28164,20 @@
       <c r="H209" s="3">
         <v>4</v>
       </c>
-      <c r="I209" s="8">
+      <c r="I209" s="7">
         <v>600000</v>
       </c>
       <c r="J209" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K209" s="4" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="L209" s="4">
         <v>0</v>
       </c>
       <c r="M209" s="4" t="s">
-        <v>2529</v>
+        <v>2526</v>
       </c>
       <c r="N209" s="4">
         <v>12</v>
@@ -28190,22 +28185,22 @@
     </row>
     <row r="210" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="6" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>2578</v>
+      </c>
+      <c r="D210" s="4" t="s">
         <v>2579</v>
-      </c>
-      <c r="B210" s="4" t="s">
-        <v>2580</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>2581</v>
-      </c>
-      <c r="D210" s="4" t="s">
-        <v>2582</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F210" s="3">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>1815</v>
@@ -28213,20 +28208,20 @@
       <c r="H210" s="3">
         <v>1</v>
       </c>
-      <c r="I210" s="8">
+      <c r="I210" s="7">
         <v>9000</v>
       </c>
       <c r="J210" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K210" s="4" t="s">
-        <v>2583</v>
+        <v>2580</v>
       </c>
       <c r="L210" s="4">
         <v>790</v>
       </c>
       <c r="M210" s="4" t="s">
-        <v>2529</v>
+        <v>2526</v>
       </c>
       <c r="N210" s="4">
         <v>2</v>
@@ -28240,16 +28235,16 @@
         <v>32</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>2584</v>
+        <v>2581</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F211" s="3">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>1815</v>
@@ -28257,7 +28252,7 @@
       <c r="H211" s="3">
         <v>3</v>
       </c>
-      <c r="I211" s="8">
+      <c r="I211" s="7">
         <v>13000</v>
       </c>
       <c r="J211" s="5" t="s">
@@ -28270,7 +28265,7 @@
         <v>140</v>
       </c>
       <c r="M211" s="4" t="s">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="N211" s="4">
         <v>12</v>
@@ -28284,16 +28279,16 @@
         <v>48</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>2587</v>
+        <v>2584</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F212" s="7">
-        <v>3100</v>
+      <c r="F212" s="15">
+        <v>3283</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>1836</v>
@@ -28301,20 +28296,20 @@
       <c r="H212" s="3">
         <v>1</v>
       </c>
-      <c r="I212" s="8">
+      <c r="I212" s="7">
         <v>120000</v>
       </c>
       <c r="J212" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K212" s="4" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="L212" s="4">
         <v>565</v>
       </c>
       <c r="M212" s="4" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="N212" s="4">
         <v>1</v>
@@ -28322,22 +28317,22 @@
     </row>
     <row r="213" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="6" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>1254</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>2590</v>
+        <v>2587</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>2591</v>
+        <v>2588</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>1814</v>
       </c>
       <c r="F213" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>1815</v>
@@ -28345,20 +28340,20 @@
       <c r="H213" s="3">
         <v>1</v>
       </c>
-      <c r="I213" s="8">
+      <c r="I213" s="7">
         <v>8000</v>
       </c>
       <c r="J213" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K213" s="4" t="s">
-        <v>2592</v>
+        <v>2589</v>
       </c>
       <c r="L213" s="4">
         <v>845</v>
       </c>
       <c r="M213" s="4" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="N213" s="4">
         <v>21</v>
@@ -28372,16 +28367,16 @@
         <v>32</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>2593</v>
+        <v>2590</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>2594</v>
+        <v>2591</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F214" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G214" s="4" t="s">
         <v>1815</v>
@@ -28389,7 +28384,7 @@
       <c r="H214" s="3">
         <v>1</v>
       </c>
-      <c r="I214" s="8">
+      <c r="I214" s="7">
         <v>1700</v>
       </c>
       <c r="J214" s="5" t="s">
@@ -28402,7 +28397,7 @@
         <v>275</v>
       </c>
       <c r="M214" s="4" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="N214" s="4">
         <v>1</v>
@@ -28416,16 +28411,16 @@
         <v>253</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>2595</v>
+        <v>2592</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>2596</v>
+        <v>2593</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F215" s="3">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>1808</v>
@@ -28433,20 +28428,20 @@
       <c r="H215" s="3">
         <v>1</v>
       </c>
-      <c r="I215" s="8">
+      <c r="I215" s="7">
         <v>40000</v>
       </c>
       <c r="J215" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K215" s="4" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="L215" s="4">
         <v>100</v>
       </c>
       <c r="M215" s="4" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="N215" s="4">
         <v>1</v>
@@ -28454,22 +28449,22 @@
     </row>
     <row r="216" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="6" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>2599</v>
+        <v>2596</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>1807</v>
       </c>
       <c r="F216" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>1815</v>
@@ -28504,16 +28499,16 @@
         <v>758</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>2601</v>
+        <v>2598</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>2602</v>
+        <v>2599</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>1807</v>
       </c>
-      <c r="F217" s="7">
-        <v>1666</v>
+      <c r="F217" s="15">
+        <v>1601</v>
       </c>
       <c r="G217" s="4" t="s">
         <v>1836</v>
@@ -28521,20 +28516,20 @@
       <c r="H217" s="3">
         <v>2</v>
       </c>
-      <c r="I217" s="8">
+      <c r="I217" s="7">
         <v>1600000</v>
       </c>
       <c r="J217" s="5" t="s">
         <v>1809</v>
       </c>
       <c r="K217" s="4" t="s">
-        <v>2603</v>
+        <v>2600</v>
       </c>
       <c r="L217" s="4">
         <v>0</v>
       </c>
       <c r="M217" s="4" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="N217" s="4">
         <v>2</v>
